--- a/progress/SLR/screening_sheet.xlsx
+++ b/progress/SLR/screening_sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git2026\research-progress\progress\SLR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96E6E2EF-C729-453B-B6C4-99F9E5CDED6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E20DB3C-9DB1-46D5-B534-217735023D37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4620" yWindow="1800" windowWidth="30720" windowHeight="18050" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3611" uniqueCount="3182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3681" uniqueCount="3183">
   <si>
     <t>screen_id</t>
   </si>
@@ -9567,13 +9567,16 @@
   </si>
   <si>
     <t>not able to identify whether bus system or railbased system public transport</t>
+  </si>
+  <si>
+    <t>keep this for actual issues to help developing background of the study later, not for SLR</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -9585,6 +9588,13 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -9612,11 +9622,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -9922,7 +9935,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K602"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="7" customWidth="1"/>
@@ -9937,7 +9950,7 @@
     <col min="11" max="11" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9972,7 +9985,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
@@ -9999,7 +10012,7 @@
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
     </row>
-    <row r="3" spans="1:11" ht="275.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="275.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>17</v>
       </c>
@@ -10032,7 +10045,7 @@
         <v>3176</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="304.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="304.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>23</v>
       </c>
@@ -10063,7 +10076,7 @@
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
     </row>
-    <row r="5" spans="1:11" ht="87" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="87" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>29</v>
       </c>
@@ -10092,7 +10105,7 @@
       </c>
       <c r="K5" s="3"/>
     </row>
-    <row r="6" spans="1:11" ht="333.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="333.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>34</v>
       </c>
@@ -10123,7 +10136,7 @@
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
     </row>
-    <row r="7" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>40</v>
       </c>
@@ -10154,7 +10167,7 @@
       </c>
       <c r="K7" s="3"/>
     </row>
-    <row r="8" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>46</v>
       </c>
@@ -10185,7 +10198,7 @@
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
     </row>
-    <row r="9" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>52</v>
       </c>
@@ -10214,7 +10227,7 @@
       </c>
       <c r="K9" s="3"/>
     </row>
-    <row r="10" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>57</v>
       </c>
@@ -10245,7 +10258,7 @@
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
     </row>
-    <row r="11" spans="1:11" ht="115.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="116" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>63</v>
       </c>
@@ -10276,7 +10289,7 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
     </row>
-    <row r="12" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>69</v>
       </c>
@@ -10307,7 +10320,7 @@
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
     </row>
-    <row r="13" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>75</v>
       </c>
@@ -10338,7 +10351,7 @@
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
     </row>
-    <row r="14" spans="1:11" ht="115.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="116" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>81</v>
       </c>
@@ -10369,7 +10382,7 @@
       </c>
       <c r="K14" s="3"/>
     </row>
-    <row r="15" spans="1:11" ht="275.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="275.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>87</v>
       </c>
@@ -10398,7 +10411,7 @@
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
     </row>
-    <row r="16" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>92</v>
       </c>
@@ -10429,7 +10442,7 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
     </row>
-    <row r="17" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>98</v>
       </c>
@@ -10458,7 +10471,7 @@
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
     </row>
-    <row r="18" spans="1:11" ht="275.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" ht="275.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>103</v>
       </c>
@@ -10489,7 +10502,7 @@
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
     </row>
-    <row r="19" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>109</v>
       </c>
@@ -10520,7 +10533,7 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
     </row>
-    <row r="20" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>115</v>
       </c>
@@ -10551,7 +10564,7 @@
       </c>
       <c r="K20" s="3"/>
     </row>
-    <row r="21" spans="1:11" ht="275.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" ht="275.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>121</v>
       </c>
@@ -10582,7 +10595,7 @@
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
     </row>
-    <row r="22" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>127</v>
       </c>
@@ -10613,7 +10626,7 @@
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
     </row>
-    <row r="23" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>133</v>
       </c>
@@ -10644,7 +10657,7 @@
       </c>
       <c r="K23" s="3"/>
     </row>
-    <row r="24" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>139</v>
       </c>
@@ -10673,7 +10686,7 @@
       </c>
       <c r="K24" s="3"/>
     </row>
-    <row r="25" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>144</v>
       </c>
@@ -10704,7 +10717,7 @@
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
     </row>
-    <row r="26" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
         <v>150</v>
       </c>
@@ -10733,7 +10746,7 @@
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
     </row>
-    <row r="27" spans="1:11" ht="319.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" ht="319" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>155</v>
       </c>
@@ -10764,7 +10777,7 @@
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
     </row>
-    <row r="28" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>161</v>
       </c>
@@ -10793,7 +10806,7 @@
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
     </row>
-    <row r="29" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>165</v>
       </c>
@@ -10822,7 +10835,7 @@
       </c>
       <c r="K29" s="3"/>
     </row>
-    <row r="30" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
         <v>169</v>
       </c>
@@ -10851,7 +10864,7 @@
       </c>
       <c r="K30" s="3"/>
     </row>
-    <row r="31" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
         <v>173</v>
       </c>
@@ -10882,7 +10895,7 @@
       </c>
       <c r="K31" s="3"/>
     </row>
-    <row r="32" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>178</v>
       </c>
@@ -10913,7 +10926,7 @@
       <c r="J32" s="3"/>
       <c r="K32" s="3"/>
     </row>
-    <row r="33" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>184</v>
       </c>
@@ -10944,7 +10957,7 @@
       <c r="J33" s="3"/>
       <c r="K33" s="3"/>
     </row>
-    <row r="34" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
         <v>189</v>
       </c>
@@ -10973,7 +10986,7 @@
       </c>
       <c r="K34" s="3"/>
     </row>
-    <row r="35" spans="1:11" ht="275.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" ht="275.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>193</v>
       </c>
@@ -11004,7 +11017,7 @@
       <c r="J35" s="3"/>
       <c r="K35" s="3"/>
     </row>
-    <row r="36" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
         <v>198</v>
       </c>
@@ -11035,7 +11048,7 @@
       </c>
       <c r="K36" s="3"/>
     </row>
-    <row r="37" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>203</v>
       </c>
@@ -11064,7 +11077,7 @@
       <c r="J37" s="3"/>
       <c r="K37" s="3"/>
     </row>
-    <row r="38" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
         <v>208</v>
       </c>
@@ -11093,7 +11106,7 @@
       </c>
       <c r="K38" s="3"/>
     </row>
-    <row r="39" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
         <v>212</v>
       </c>
@@ -11122,7 +11135,7 @@
       </c>
       <c r="K39" s="3"/>
     </row>
-    <row r="40" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
         <v>217</v>
       </c>
@@ -11153,7 +11166,7 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
     </row>
-    <row r="41" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
         <v>223</v>
       </c>
@@ -11182,7 +11195,7 @@
       <c r="J41" s="3"/>
       <c r="K41" s="3"/>
     </row>
-    <row r="42" spans="1:11" ht="333.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" ht="333.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
         <v>228</v>
       </c>
@@ -11213,7 +11226,7 @@
       <c r="J42" s="3"/>
       <c r="K42" s="3"/>
     </row>
-    <row r="43" spans="1:11" ht="275.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" ht="275.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
         <v>234</v>
       </c>
@@ -11244,7 +11257,7 @@
       </c>
       <c r="K43" s="3"/>
     </row>
-    <row r="44" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
         <v>240</v>
       </c>
@@ -11275,7 +11288,7 @@
       <c r="J44" s="3"/>
       <c r="K44" s="3"/>
     </row>
-    <row r="45" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
         <v>246</v>
       </c>
@@ -11306,7 +11319,7 @@
       <c r="J45" s="3"/>
       <c r="K45" s="3"/>
     </row>
-    <row r="46" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
         <v>252</v>
       </c>
@@ -11337,7 +11350,7 @@
       <c r="J46" s="3"/>
       <c r="K46" s="3"/>
     </row>
-    <row r="47" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
         <v>258</v>
       </c>
@@ -11366,7 +11379,7 @@
       </c>
       <c r="K47" s="3"/>
     </row>
-    <row r="48" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
         <v>262</v>
       </c>
@@ -11397,7 +11410,7 @@
       </c>
       <c r="K48" s="3"/>
     </row>
-    <row r="49" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
         <v>267</v>
       </c>
@@ -11426,7 +11439,7 @@
       <c r="J49" s="3"/>
       <c r="K49" s="3"/>
     </row>
-    <row r="50" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
         <v>272</v>
       </c>
@@ -11457,7 +11470,7 @@
       </c>
       <c r="K50" s="3"/>
     </row>
-    <row r="51" spans="1:11" ht="275.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" ht="275.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
         <v>278</v>
       </c>
@@ -11486,7 +11499,7 @@
       <c r="J51" s="3"/>
       <c r="K51" s="3"/>
     </row>
-    <row r="52" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="3" t="s">
         <v>283</v>
       </c>
@@ -11517,7 +11530,7 @@
         <v>3181</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
         <v>289</v>
       </c>
@@ -11548,7 +11561,7 @@
       </c>
       <c r="K53" s="3"/>
     </row>
-    <row r="54" spans="1:11" ht="275.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" ht="275.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="s">
         <v>295</v>
       </c>
@@ -11579,7 +11592,7 @@
       <c r="J54" s="3"/>
       <c r="K54" s="3"/>
     </row>
-    <row r="55" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
         <v>301</v>
       </c>
@@ -11610,7 +11623,7 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
     </row>
-    <row r="56" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
         <v>307</v>
       </c>
@@ -11641,7 +11654,7 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
     </row>
-    <row r="57" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
         <v>313</v>
       </c>
@@ -11670,7 +11683,7 @@
       <c r="J57" s="3"/>
       <c r="K57" s="3"/>
     </row>
-    <row r="58" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="3" t="s">
         <v>317</v>
       </c>
@@ -11701,7 +11714,7 @@
       <c r="J58" s="3"/>
       <c r="K58" s="3"/>
     </row>
-    <row r="59" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
         <v>322</v>
       </c>
@@ -11732,7 +11745,7 @@
         <v>3181</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="275.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" ht="275.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="3" t="s">
         <v>327</v>
       </c>
@@ -11763,7 +11776,7 @@
       <c r="J60" s="3"/>
       <c r="K60" s="3"/>
     </row>
-    <row r="61" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="3" t="s">
         <v>333</v>
       </c>
@@ -11794,7 +11807,7 @@
       <c r="J61" s="3"/>
       <c r="K61" s="3"/>
     </row>
-    <row r="62" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="3" t="s">
         <v>339</v>
       </c>
@@ -11825,7 +11838,7 @@
       </c>
       <c r="K62" s="3"/>
     </row>
-    <row r="63" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="3" t="s">
         <v>345</v>
       </c>
@@ -11856,7 +11869,7 @@
       <c r="J63" s="3"/>
       <c r="K63" s="3"/>
     </row>
-    <row r="64" spans="1:11" ht="275.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" ht="275.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="3" t="s">
         <v>351</v>
       </c>
@@ -11887,7 +11900,7 @@
       <c r="J64" s="3"/>
       <c r="K64" s="3"/>
     </row>
-    <row r="65" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="3" t="s">
         <v>357</v>
       </c>
@@ -11909,12 +11922,16 @@
       <c r="G65" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="H65" s="3"/>
-      <c r="I65" s="3"/>
+      <c r="H65" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="J65" s="3"/>
       <c r="K65" s="3"/>
     </row>
-    <row r="66" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="3" t="s">
         <v>363</v>
       </c>
@@ -11936,12 +11953,16 @@
       <c r="G66" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="H66" s="3"/>
-      <c r="I66" s="3"/>
+      <c r="H66" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="J66" s="3"/>
       <c r="K66" s="3"/>
     </row>
-    <row r="67" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="3" t="s">
         <v>369</v>
       </c>
@@ -11963,12 +11984,16 @@
       <c r="G67" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="H67" s="3"/>
-      <c r="I67" s="3"/>
+      <c r="H67" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
     </row>
-    <row r="68" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="3" t="s">
         <v>375</v>
       </c>
@@ -11988,12 +12013,18 @@
         <v>378</v>
       </c>
       <c r="G68" s="3"/>
-      <c r="H68" s="3"/>
-      <c r="I68" s="3"/>
+      <c r="H68" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="J68" s="3"/>
-      <c r="K68" s="3"/>
-    </row>
-    <row r="69" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K68" s="3" t="s">
+        <v>3182</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="3" t="s">
         <v>379</v>
       </c>
@@ -12015,12 +12046,16 @@
       <c r="G69" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="H69" s="3"/>
+      <c r="H69" s="3" t="s">
+        <v>3177</v>
+      </c>
       <c r="I69" s="3"/>
-      <c r="J69" s="3"/>
+      <c r="J69" s="3" t="s">
+        <v>3178</v>
+      </c>
       <c r="K69" s="3"/>
     </row>
-    <row r="70" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="3" t="s">
         <v>385</v>
       </c>
@@ -12042,12 +12077,16 @@
       <c r="G70" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="H70" s="3"/>
+      <c r="H70" s="3" t="s">
+        <v>3179</v>
+      </c>
       <c r="I70" s="3"/>
       <c r="J70" s="3"/>
-      <c r="K70" s="3"/>
-    </row>
-    <row r="71" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K70" s="3" t="s">
+        <v>3181</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="3" t="s">
         <v>391</v>
       </c>
@@ -12069,12 +12108,16 @@
       <c r="G71" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="H71" s="3"/>
-      <c r="I71" s="3"/>
+      <c r="H71" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="J71" s="3"/>
       <c r="K71" s="3"/>
     </row>
-    <row r="72" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="3" t="s">
         <v>397</v>
       </c>
@@ -12094,12 +12137,18 @@
         <v>400</v>
       </c>
       <c r="G72" s="3"/>
-      <c r="H72" s="3"/>
-      <c r="I72" s="3"/>
+      <c r="H72" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="J72" s="3"/>
-      <c r="K72" s="3"/>
-    </row>
-    <row r="73" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K72" s="3" t="s">
+        <v>3182</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="3" t="s">
         <v>401</v>
       </c>
@@ -12119,12 +12168,16 @@
         <v>405</v>
       </c>
       <c r="G73" s="3"/>
-      <c r="H73" s="3"/>
-      <c r="I73" s="3"/>
+      <c r="H73" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>3171</v>
+      </c>
       <c r="J73" s="3"/>
       <c r="K73" s="3"/>
     </row>
-    <row r="74" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="3" t="s">
         <v>406</v>
       </c>
@@ -12146,12 +12199,16 @@
       <c r="G74" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="H74" s="3"/>
+      <c r="H74" s="3" t="s">
+        <v>3179</v>
+      </c>
       <c r="I74" s="3"/>
-      <c r="J74" s="3"/>
+      <c r="J74" s="3" t="s">
+        <v>3178</v>
+      </c>
       <c r="K74" s="3"/>
     </row>
-    <row r="75" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="3" t="s">
         <v>412</v>
       </c>
@@ -12173,12 +12230,16 @@
       <c r="G75" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="H75" s="3"/>
-      <c r="I75" s="3"/>
+      <c r="H75" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="J75" s="3"/>
       <c r="K75" s="3"/>
     </row>
-    <row r="76" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="3" t="s">
         <v>417</v>
       </c>
@@ -12198,12 +12259,16 @@
         <v>420</v>
       </c>
       <c r="G76" s="3"/>
-      <c r="H76" s="3"/>
-      <c r="I76" s="3"/>
+      <c r="H76" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="J76" s="3"/>
       <c r="K76" s="3"/>
     </row>
-    <row r="77" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="3" t="s">
         <v>421</v>
       </c>
@@ -12225,12 +12290,16 @@
       <c r="G77" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="H77" s="3"/>
-      <c r="I77" s="3"/>
+      <c r="H77" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="J77" s="3"/>
       <c r="K77" s="3"/>
     </row>
-    <row r="78" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="3" t="s">
         <v>427</v>
       </c>
@@ -12252,12 +12321,16 @@
       <c r="G78" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="H78" s="3"/>
+      <c r="H78" s="3" t="s">
+        <v>3179</v>
+      </c>
       <c r="I78" s="3"/>
-      <c r="J78" s="3"/>
+      <c r="J78" s="3" t="s">
+        <v>3180</v>
+      </c>
       <c r="K78" s="3"/>
     </row>
-    <row r="79" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="3" t="s">
         <v>433</v>
       </c>
@@ -12279,12 +12352,16 @@
       <c r="G79" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="H79" s="3"/>
-      <c r="I79" s="3"/>
+      <c r="H79" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="J79" s="3"/>
       <c r="K79" s="3"/>
     </row>
-    <row r="80" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="3" t="s">
         <v>438</v>
       </c>
@@ -12306,12 +12383,16 @@
       <c r="G80" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="H80" s="3"/>
+      <c r="H80" s="3" t="s">
+        <v>3177</v>
+      </c>
       <c r="I80" s="3"/>
-      <c r="J80" s="3"/>
+      <c r="J80" s="3" t="s">
+        <v>3180</v>
+      </c>
       <c r="K80" s="3"/>
     </row>
-    <row r="81" spans="1:11" ht="319.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:11" ht="319" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="3" t="s">
         <v>444</v>
       </c>
@@ -12333,12 +12414,16 @@
       <c r="G81" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="H81" s="3"/>
-      <c r="I81" s="3"/>
+      <c r="H81" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="J81" s="3"/>
       <c r="K81" s="3"/>
     </row>
-    <row r="82" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="3" t="s">
         <v>449</v>
       </c>
@@ -12360,12 +12445,16 @@
       <c r="G82" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="H82" s="3"/>
-      <c r="I82" s="3"/>
+      <c r="H82" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>3170</v>
+      </c>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
     </row>
-    <row r="83" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="3" t="s">
         <v>455</v>
       </c>
@@ -12385,12 +12474,16 @@
         <v>459</v>
       </c>
       <c r="G83" s="3"/>
-      <c r="H83" s="3"/>
-      <c r="I83" s="3"/>
+      <c r="H83" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3170</v>
+      </c>
       <c r="J83" s="3"/>
       <c r="K83" s="3"/>
     </row>
-    <row r="84" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="3" t="s">
         <v>460</v>
       </c>
@@ -12412,12 +12505,16 @@
       <c r="G84" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="H84" s="3"/>
-      <c r="I84" s="3"/>
+      <c r="H84" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>3170</v>
+      </c>
       <c r="J84" s="3"/>
       <c r="K84" s="3"/>
     </row>
-    <row r="85" spans="1:11" ht="115.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:11" ht="116" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="3" t="s">
         <v>465</v>
       </c>
@@ -12439,12 +12536,16 @@
       <c r="G85" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="H85" s="3"/>
-      <c r="I85" s="3"/>
+      <c r="H85" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>3170</v>
+      </c>
       <c r="J85" s="3"/>
       <c r="K85" s="3"/>
     </row>
-    <row r="86" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="3" t="s">
         <v>471</v>
       </c>
@@ -12466,12 +12567,16 @@
       <c r="G86" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="H86" s="3"/>
+      <c r="H86" s="3" t="s">
+        <v>3179</v>
+      </c>
       <c r="I86" s="3"/>
-      <c r="J86" s="3"/>
+      <c r="J86" s="3" t="s">
+        <v>3178</v>
+      </c>
       <c r="K86" s="3"/>
     </row>
-    <row r="87" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="3" t="s">
         <v>476</v>
       </c>
@@ -12493,12 +12598,16 @@
       <c r="G87" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="H87" s="3"/>
-      <c r="I87" s="3"/>
+      <c r="H87" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="J87" s="3"/>
       <c r="K87" s="3"/>
     </row>
-    <row r="88" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="3" t="s">
         <v>482</v>
       </c>
@@ -12520,12 +12629,16 @@
       <c r="G88" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="H88" s="3"/>
+      <c r="H88" s="3" t="s">
+        <v>3179</v>
+      </c>
       <c r="I88" s="3"/>
-      <c r="J88" s="3"/>
+      <c r="J88" s="3" t="s">
+        <v>3178</v>
+      </c>
       <c r="K88" s="3"/>
     </row>
-    <row r="89" spans="1:11" ht="319.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:11" ht="319" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="3" t="s">
         <v>487</v>
       </c>
@@ -12547,12 +12660,16 @@
       <c r="G89" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="H89" s="3"/>
-      <c r="I89" s="3"/>
+      <c r="H89" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="J89" s="3"/>
       <c r="K89" s="3"/>
     </row>
-    <row r="90" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="3" t="s">
         <v>492</v>
       </c>
@@ -12574,12 +12691,16 @@
       <c r="G90" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="H90" s="3"/>
+      <c r="H90" s="3" t="s">
+        <v>3177</v>
+      </c>
       <c r="I90" s="3"/>
-      <c r="J90" s="3"/>
+      <c r="J90" s="3" t="s">
+        <v>3178</v>
+      </c>
       <c r="K90" s="3"/>
     </row>
-    <row r="91" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="3" t="s">
         <v>497</v>
       </c>
@@ -12601,12 +12722,16 @@
       <c r="G91" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="H91" s="3"/>
-      <c r="I91" s="3"/>
+      <c r="H91" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="J91" s="3"/>
       <c r="K91" s="3"/>
     </row>
-    <row r="92" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="3" t="s">
         <v>503</v>
       </c>
@@ -12628,12 +12753,16 @@
       <c r="G92" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="H92" s="3"/>
+      <c r="H92" s="3" t="s">
+        <v>3179</v>
+      </c>
       <c r="I92" s="3"/>
-      <c r="J92" s="3"/>
+      <c r="J92" s="3" t="s">
+        <v>3180</v>
+      </c>
       <c r="K92" s="3"/>
     </row>
-    <row r="93" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="3" t="s">
         <v>509</v>
       </c>
@@ -12655,12 +12784,16 @@
       <c r="G93" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="H93" s="3"/>
+      <c r="H93" s="3" t="s">
+        <v>3179</v>
+      </c>
       <c r="I93" s="3"/>
       <c r="J93" s="3"/>
-      <c r="K93" s="3"/>
-    </row>
-    <row r="94" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K93" s="4" t="s">
+        <v>3181</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="3" t="s">
         <v>515</v>
       </c>
@@ -12682,12 +12815,16 @@
       <c r="G94" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="H94" s="3"/>
-      <c r="I94" s="3"/>
+      <c r="H94" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="J94" s="3"/>
       <c r="K94" s="3"/>
     </row>
-    <row r="95" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="3" t="s">
         <v>520</v>
       </c>
@@ -12707,12 +12844,16 @@
         <v>523</v>
       </c>
       <c r="G95" s="3"/>
-      <c r="H95" s="3"/>
+      <c r="H95" s="3" t="s">
+        <v>3177</v>
+      </c>
       <c r="I95" s="3"/>
-      <c r="J95" s="3"/>
+      <c r="J95" s="3" t="s">
+        <v>3180</v>
+      </c>
       <c r="K95" s="3"/>
     </row>
-    <row r="96" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="3" t="s">
         <v>524</v>
       </c>
@@ -12734,12 +12875,16 @@
       <c r="G96" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="H96" s="3"/>
-      <c r="I96" s="3"/>
+      <c r="H96" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="J96" s="3"/>
       <c r="K96" s="3"/>
     </row>
-    <row r="97" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="3" t="s">
         <v>530</v>
       </c>
@@ -12759,12 +12904,16 @@
         <v>534</v>
       </c>
       <c r="G97" s="3"/>
-      <c r="H97" s="3"/>
+      <c r="H97" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="I97" s="3"/>
       <c r="J97" s="3"/>
-      <c r="K97" s="3"/>
-    </row>
-    <row r="98" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K97" s="4" t="s">
+        <v>3182</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="3" t="s">
         <v>535</v>
       </c>
@@ -12784,12 +12933,16 @@
         <v>538</v>
       </c>
       <c r="G98" s="3"/>
-      <c r="H98" s="3"/>
-      <c r="I98" s="3"/>
+      <c r="H98" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="J98" s="3"/>
       <c r="K98" s="3"/>
     </row>
-    <row r="99" spans="1:11" ht="275.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11" ht="275.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="3" t="s">
         <v>539</v>
       </c>
@@ -12816,7 +12969,7 @@
       <c r="J99" s="3"/>
       <c r="K99" s="3"/>
     </row>
-    <row r="100" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="3" t="s">
         <v>544</v>
       </c>
@@ -12843,7 +12996,7 @@
       <c r="J100" s="3"/>
       <c r="K100" s="3"/>
     </row>
-    <row r="101" spans="1:11" ht="87" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11" ht="87" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="3" t="s">
         <v>549</v>
       </c>
@@ -12868,7 +13021,7 @@
       <c r="J101" s="3"/>
       <c r="K101" s="3"/>
     </row>
-    <row r="102" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="3" t="s">
         <v>554</v>
       </c>
@@ -12893,7 +13046,7 @@
       <c r="J102" s="3"/>
       <c r="K102" s="3"/>
     </row>
-    <row r="103" spans="1:11" ht="275.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11" ht="275.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="3" t="s">
         <v>558</v>
       </c>
@@ -12920,7 +13073,7 @@
       <c r="J103" s="3"/>
       <c r="K103" s="3"/>
     </row>
-    <row r="104" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="3" t="s">
         <v>564</v>
       </c>
@@ -12947,7 +13100,7 @@
       <c r="J104" s="3"/>
       <c r="K104" s="3"/>
     </row>
-    <row r="105" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="3" t="s">
         <v>569</v>
       </c>
@@ -12974,7 +13127,7 @@
       <c r="J105" s="3"/>
       <c r="K105" s="3"/>
     </row>
-    <row r="106" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="3" t="s">
         <v>575</v>
       </c>
@@ -12999,7 +13152,7 @@
       <c r="J106" s="3"/>
       <c r="K106" s="3"/>
     </row>
-    <row r="107" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="3" t="s">
         <v>580</v>
       </c>
@@ -13024,7 +13177,7 @@
       <c r="J107" s="3"/>
       <c r="K107" s="3"/>
     </row>
-    <row r="108" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="3" t="s">
         <v>584</v>
       </c>
@@ -13051,7 +13204,7 @@
       <c r="J108" s="3"/>
       <c r="K108" s="3"/>
     </row>
-    <row r="109" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="3" t="s">
         <v>589</v>
       </c>
@@ -13078,7 +13231,7 @@
       <c r="J109" s="3"/>
       <c r="K109" s="3"/>
     </row>
-    <row r="110" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="3" t="s">
         <v>595</v>
       </c>
@@ -13105,7 +13258,7 @@
       <c r="J110" s="3"/>
       <c r="K110" s="3"/>
     </row>
-    <row r="111" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="3" t="s">
         <v>601</v>
       </c>
@@ -13132,7 +13285,7 @@
       <c r="J111" s="3"/>
       <c r="K111" s="3"/>
     </row>
-    <row r="112" spans="1:11" ht="275.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11" ht="275.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="3" t="s">
         <v>607</v>
       </c>
@@ -13159,7 +13312,7 @@
       <c r="J112" s="3"/>
       <c r="K112" s="3"/>
     </row>
-    <row r="113" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="3" t="s">
         <v>613</v>
       </c>
@@ -13186,7 +13339,7 @@
       <c r="J113" s="3"/>
       <c r="K113" s="3"/>
     </row>
-    <row r="114" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="3" t="s">
         <v>618</v>
       </c>
@@ -13211,7 +13364,7 @@
       <c r="J114" s="3"/>
       <c r="K114" s="3"/>
     </row>
-    <row r="115" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="3" t="s">
         <v>622</v>
       </c>
@@ -13238,7 +13391,7 @@
       <c r="J115" s="3"/>
       <c r="K115" s="3"/>
     </row>
-    <row r="116" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="3" t="s">
         <v>627</v>
       </c>
@@ -13263,7 +13416,7 @@
       <c r="J116" s="3"/>
       <c r="K116" s="3"/>
     </row>
-    <row r="117" spans="1:11" ht="101.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:11" ht="101.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="3" t="s">
         <v>632</v>
       </c>
@@ -13290,7 +13443,7 @@
       <c r="J117" s="3"/>
       <c r="K117" s="3"/>
     </row>
-    <row r="118" spans="1:11" ht="115.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:11" ht="116" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="3" t="s">
         <v>637</v>
       </c>
@@ -13317,7 +13470,7 @@
       <c r="J118" s="3"/>
       <c r="K118" s="3"/>
     </row>
-    <row r="119" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="3" t="s">
         <v>642</v>
       </c>
@@ -13344,7 +13497,7 @@
       <c r="J119" s="3"/>
       <c r="K119" s="3"/>
     </row>
-    <row r="120" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="3" t="s">
         <v>647</v>
       </c>
@@ -13371,7 +13524,7 @@
       <c r="J120" s="3"/>
       <c r="K120" s="3"/>
     </row>
-    <row r="121" spans="1:11" ht="101.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:11" ht="101.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="3" t="s">
         <v>653</v>
       </c>
@@ -13398,7 +13551,7 @@
       <c r="J121" s="3"/>
       <c r="K121" s="3"/>
     </row>
-    <row r="122" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="3" t="s">
         <v>659</v>
       </c>
@@ -13423,7 +13576,7 @@
       <c r="J122" s="3"/>
       <c r="K122" s="3"/>
     </row>
-    <row r="123" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="3" t="s">
         <v>664</v>
       </c>
@@ -13450,7 +13603,7 @@
       <c r="J123" s="3"/>
       <c r="K123" s="3"/>
     </row>
-    <row r="124" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="3" t="s">
         <v>670</v>
       </c>
@@ -13475,7 +13628,7 @@
       <c r="J124" s="3"/>
       <c r="K124" s="3"/>
     </row>
-    <row r="125" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="3" t="s">
         <v>675</v>
       </c>
@@ -13502,7 +13655,7 @@
       <c r="J125" s="3"/>
       <c r="K125" s="3"/>
     </row>
-    <row r="126" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="3" t="s">
         <v>681</v>
       </c>
@@ -13529,7 +13682,7 @@
       <c r="J126" s="3"/>
       <c r="K126" s="3"/>
     </row>
-    <row r="127" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="3" t="s">
         <v>687</v>
       </c>
@@ -13556,7 +13709,7 @@
       <c r="J127" s="3"/>
       <c r="K127" s="3"/>
     </row>
-    <row r="128" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="3" t="s">
         <v>693</v>
       </c>
@@ -13583,7 +13736,7 @@
       <c r="J128" s="3"/>
       <c r="K128" s="3"/>
     </row>
-    <row r="129" spans="1:11" ht="275.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:11" ht="275.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="3" t="s">
         <v>698</v>
       </c>
@@ -13610,7 +13763,7 @@
       <c r="J129" s="3"/>
       <c r="K129" s="3"/>
     </row>
-    <row r="130" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="3" t="s">
         <v>704</v>
       </c>
@@ -13637,7 +13790,7 @@
       <c r="J130" s="3"/>
       <c r="K130" s="3"/>
     </row>
-    <row r="131" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="3" t="s">
         <v>710</v>
       </c>
@@ -13662,7 +13815,7 @@
       <c r="J131" s="3"/>
       <c r="K131" s="3"/>
     </row>
-    <row r="132" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="3" t="s">
         <v>715</v>
       </c>
@@ -13687,7 +13840,7 @@
       <c r="J132" s="3"/>
       <c r="K132" s="3"/>
     </row>
-    <row r="133" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="3" t="s">
         <v>720</v>
       </c>
@@ -13712,7 +13865,7 @@
       <c r="J133" s="3"/>
       <c r="K133" s="3"/>
     </row>
-    <row r="134" spans="1:11" ht="101.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:11" ht="101.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="3" t="s">
         <v>725</v>
       </c>
@@ -13739,7 +13892,7 @@
       <c r="J134" s="3"/>
       <c r="K134" s="3"/>
     </row>
-    <row r="135" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="3" t="s">
         <v>731</v>
       </c>
@@ -13766,7 +13919,7 @@
       <c r="J135" s="3"/>
       <c r="K135" s="3"/>
     </row>
-    <row r="136" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="3" t="s">
         <v>736</v>
       </c>
@@ -13791,7 +13944,7 @@
       <c r="J136" s="3"/>
       <c r="K136" s="3"/>
     </row>
-    <row r="137" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="3" t="s">
         <v>740</v>
       </c>
@@ -13816,7 +13969,7 @@
       <c r="J137" s="3"/>
       <c r="K137" s="3"/>
     </row>
-    <row r="138" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="3" t="s">
         <v>744</v>
       </c>
@@ -13841,7 +13994,7 @@
       <c r="J138" s="3"/>
       <c r="K138" s="3"/>
     </row>
-    <row r="139" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="3" t="s">
         <v>748</v>
       </c>
@@ -13866,7 +14019,7 @@
       <c r="J139" s="3"/>
       <c r="K139" s="3"/>
     </row>
-    <row r="140" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="3" t="s">
         <v>752</v>
       </c>
@@ -13893,7 +14046,7 @@
       <c r="J140" s="3"/>
       <c r="K140" s="3"/>
     </row>
-    <row r="141" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="3" t="s">
         <v>758</v>
       </c>
@@ -13918,7 +14071,7 @@
       <c r="J141" s="3"/>
       <c r="K141" s="3"/>
     </row>
-    <row r="142" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="3" t="s">
         <v>763</v>
       </c>
@@ -13945,7 +14098,7 @@
       <c r="J142" s="3"/>
       <c r="K142" s="3"/>
     </row>
-    <row r="143" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="3" t="s">
         <v>769</v>
       </c>
@@ -13972,7 +14125,7 @@
       <c r="J143" s="3"/>
       <c r="K143" s="3"/>
     </row>
-    <row r="144" spans="1:11" ht="115.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:11" ht="116" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="3" t="s">
         <v>775</v>
       </c>
@@ -13999,7 +14152,7 @@
       <c r="J144" s="3"/>
       <c r="K144" s="3"/>
     </row>
-    <row r="145" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="3" t="s">
         <v>780</v>
       </c>
@@ -14026,7 +14179,7 @@
       <c r="J145" s="3"/>
       <c r="K145" s="3"/>
     </row>
-    <row r="146" spans="1:11" ht="289.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:11" ht="290" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="3" t="s">
         <v>785</v>
       </c>
@@ -14053,7 +14206,7 @@
       <c r="J146" s="3"/>
       <c r="K146" s="3"/>
     </row>
-    <row r="147" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="3" t="s">
         <v>791</v>
       </c>
@@ -14080,7 +14233,7 @@
       <c r="J147" s="3"/>
       <c r="K147" s="3"/>
     </row>
-    <row r="148" spans="1:11" ht="289.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:11" ht="290" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="3" t="s">
         <v>797</v>
       </c>
@@ -14107,7 +14260,7 @@
       <c r="J148" s="3"/>
       <c r="K148" s="3"/>
     </row>
-    <row r="149" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="3" t="s">
         <v>803</v>
       </c>
@@ -14134,7 +14287,7 @@
       <c r="J149" s="3"/>
       <c r="K149" s="3"/>
     </row>
-    <row r="150" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="3" t="s">
         <v>808</v>
       </c>
@@ -14161,7 +14314,7 @@
       <c r="J150" s="3"/>
       <c r="K150" s="3"/>
     </row>
-    <row r="151" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="3" t="s">
         <v>814</v>
       </c>
@@ -14186,7 +14339,7 @@
       <c r="J151" s="3"/>
       <c r="K151" s="3"/>
     </row>
-    <row r="152" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="3" t="s">
         <v>818</v>
       </c>
@@ -14213,7 +14366,7 @@
       <c r="J152" s="3"/>
       <c r="K152" s="3"/>
     </row>
-    <row r="153" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="3" t="s">
         <v>823</v>
       </c>
@@ -14240,7 +14393,7 @@
       <c r="J153" s="3"/>
       <c r="K153" s="3"/>
     </row>
-    <row r="154" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="3" t="s">
         <v>828</v>
       </c>
@@ -14267,7 +14420,7 @@
       <c r="J154" s="3"/>
       <c r="K154" s="3"/>
     </row>
-    <row r="155" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="3" t="s">
         <v>833</v>
       </c>
@@ -14294,7 +14447,7 @@
       <c r="J155" s="3"/>
       <c r="K155" s="3"/>
     </row>
-    <row r="156" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="3" t="s">
         <v>839</v>
       </c>
@@ -14319,7 +14472,7 @@
       <c r="J156" s="3"/>
       <c r="K156" s="3"/>
     </row>
-    <row r="157" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="3" t="s">
         <v>843</v>
       </c>
@@ -14346,7 +14499,7 @@
       <c r="J157" s="3"/>
       <c r="K157" s="3"/>
     </row>
-    <row r="158" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="3" t="s">
         <v>848</v>
       </c>
@@ -14373,7 +14526,7 @@
       <c r="J158" s="3"/>
       <c r="K158" s="3"/>
     </row>
-    <row r="159" spans="1:11" ht="333.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:11" ht="333.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="3" t="s">
         <v>854</v>
       </c>
@@ -14400,7 +14553,7 @@
       <c r="J159" s="3"/>
       <c r="K159" s="3"/>
     </row>
-    <row r="160" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="3" t="s">
         <v>859</v>
       </c>
@@ -14425,7 +14578,7 @@
       <c r="J160" s="3"/>
       <c r="K160" s="3"/>
     </row>
-    <row r="161" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="3" t="s">
         <v>864</v>
       </c>
@@ -14452,7 +14605,7 @@
       <c r="J161" s="3"/>
       <c r="K161" s="3"/>
     </row>
-    <row r="162" spans="1:11" ht="115.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:11" ht="116" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="3" t="s">
         <v>869</v>
       </c>
@@ -14479,7 +14632,7 @@
       <c r="J162" s="3"/>
       <c r="K162" s="3"/>
     </row>
-    <row r="163" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="3" t="s">
         <v>875</v>
       </c>
@@ -14504,7 +14657,7 @@
       <c r="J163" s="3"/>
       <c r="K163" s="3"/>
     </row>
-    <row r="164" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="3" t="s">
         <v>879</v>
       </c>
@@ -14531,7 +14684,7 @@
       <c r="J164" s="3"/>
       <c r="K164" s="3"/>
     </row>
-    <row r="165" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="3" t="s">
         <v>884</v>
       </c>
@@ -14558,7 +14711,7 @@
       <c r="J165" s="3"/>
       <c r="K165" s="3"/>
     </row>
-    <row r="166" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="3" t="s">
         <v>890</v>
       </c>
@@ -14585,7 +14738,7 @@
       <c r="J166" s="3"/>
       <c r="K166" s="3"/>
     </row>
-    <row r="167" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="3" t="s">
         <v>895</v>
       </c>
@@ -14612,7 +14765,7 @@
       <c r="J167" s="3"/>
       <c r="K167" s="3"/>
     </row>
-    <row r="168" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="3" t="s">
         <v>901</v>
       </c>
@@ -14639,7 +14792,7 @@
       <c r="J168" s="3"/>
       <c r="K168" s="3"/>
     </row>
-    <row r="169" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="3" t="s">
         <v>907</v>
       </c>
@@ -14666,7 +14819,7 @@
       <c r="J169" s="3"/>
       <c r="K169" s="3"/>
     </row>
-    <row r="170" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="3" t="s">
         <v>913</v>
       </c>
@@ -14693,7 +14846,7 @@
       <c r="J170" s="3"/>
       <c r="K170" s="3"/>
     </row>
-    <row r="171" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="3" t="s">
         <v>918</v>
       </c>
@@ -14720,7 +14873,7 @@
       <c r="J171" s="3"/>
       <c r="K171" s="3"/>
     </row>
-    <row r="172" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="3" t="s">
         <v>924</v>
       </c>
@@ -14747,7 +14900,7 @@
       <c r="J172" s="3"/>
       <c r="K172" s="3"/>
     </row>
-    <row r="173" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="3" t="s">
         <v>930</v>
       </c>
@@ -14774,7 +14927,7 @@
       <c r="J173" s="3"/>
       <c r="K173" s="3"/>
     </row>
-    <row r="174" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="3" t="s">
         <v>935</v>
       </c>
@@ -14801,7 +14954,7 @@
       <c r="J174" s="3"/>
       <c r="K174" s="3"/>
     </row>
-    <row r="175" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="3" t="s">
         <v>941</v>
       </c>
@@ -14828,7 +14981,7 @@
       <c r="J175" s="3"/>
       <c r="K175" s="3"/>
     </row>
-    <row r="176" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="3" t="s">
         <v>946</v>
       </c>
@@ -14853,7 +15006,7 @@
       <c r="J176" s="3"/>
       <c r="K176" s="3"/>
     </row>
-    <row r="177" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="3" t="s">
         <v>951</v>
       </c>
@@ -14880,7 +15033,7 @@
       <c r="J177" s="3"/>
       <c r="K177" s="3"/>
     </row>
-    <row r="178" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="3" t="s">
         <v>957</v>
       </c>
@@ -14907,7 +15060,7 @@
       <c r="J178" s="3"/>
       <c r="K178" s="3"/>
     </row>
-    <row r="179" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="3" t="s">
         <v>963</v>
       </c>
@@ -14934,7 +15087,7 @@
       <c r="J179" s="3"/>
       <c r="K179" s="3"/>
     </row>
-    <row r="180" spans="1:11" ht="115.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:11" ht="116" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="3" t="s">
         <v>969</v>
       </c>
@@ -14957,7 +15110,7 @@
       <c r="J180" s="3"/>
       <c r="K180" s="3"/>
     </row>
-    <row r="181" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="3" t="s">
         <v>973</v>
       </c>
@@ -14984,7 +15137,7 @@
       <c r="J181" s="3"/>
       <c r="K181" s="3"/>
     </row>
-    <row r="182" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="3" t="s">
         <v>979</v>
       </c>
@@ -15009,7 +15162,7 @@
       <c r="J182" s="3"/>
       <c r="K182" s="3"/>
     </row>
-    <row r="183" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="3" t="s">
         <v>983</v>
       </c>
@@ -15036,7 +15189,7 @@
       <c r="J183" s="3"/>
       <c r="K183" s="3"/>
     </row>
-    <row r="184" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="3" t="s">
         <v>988</v>
       </c>
@@ -15063,7 +15216,7 @@
       <c r="J184" s="3"/>
       <c r="K184" s="3"/>
     </row>
-    <row r="185" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="3" t="s">
         <v>994</v>
       </c>
@@ -15090,7 +15243,7 @@
       <c r="J185" s="3"/>
       <c r="K185" s="3"/>
     </row>
-    <row r="186" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="3" t="s">
         <v>1000</v>
       </c>
@@ -15115,7 +15268,7 @@
       <c r="J186" s="3"/>
       <c r="K186" s="3"/>
     </row>
-    <row r="187" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="3" t="s">
         <v>1005</v>
       </c>
@@ -15142,7 +15295,7 @@
       <c r="J187" s="3"/>
       <c r="K187" s="3"/>
     </row>
-    <row r="188" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="3" t="s">
         <v>1011</v>
       </c>
@@ -15169,7 +15322,7 @@
       <c r="J188" s="3"/>
       <c r="K188" s="3"/>
     </row>
-    <row r="189" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="3" t="s">
         <v>1016</v>
       </c>
@@ -15194,7 +15347,7 @@
       <c r="J189" s="3"/>
       <c r="K189" s="3"/>
     </row>
-    <row r="190" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="3" t="s">
         <v>1020</v>
       </c>
@@ -15221,7 +15374,7 @@
       <c r="J190" s="3"/>
       <c r="K190" s="3"/>
     </row>
-    <row r="191" spans="1:11" ht="289.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:11" ht="290" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="3" t="s">
         <v>1025</v>
       </c>
@@ -15248,7 +15401,7 @@
       <c r="J191" s="3"/>
       <c r="K191" s="3"/>
     </row>
-    <row r="192" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="3" t="s">
         <v>1031</v>
       </c>
@@ -15275,7 +15428,7 @@
       <c r="J192" s="3"/>
       <c r="K192" s="3"/>
     </row>
-    <row r="193" spans="1:11" ht="101.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:11" ht="101.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="3" t="s">
         <v>1037</v>
       </c>
@@ -15300,7 +15453,7 @@
       <c r="J193" s="3"/>
       <c r="K193" s="3"/>
     </row>
-    <row r="194" spans="1:11" ht="115.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:11" ht="116" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="3" t="s">
         <v>1041</v>
       </c>
@@ -15325,7 +15478,7 @@
       <c r="J194" s="3"/>
       <c r="K194" s="3"/>
     </row>
-    <row r="195" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="3" t="s">
         <v>1046</v>
       </c>
@@ -15352,7 +15505,7 @@
       <c r="J195" s="3"/>
       <c r="K195" s="3"/>
     </row>
-    <row r="196" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="3" t="s">
         <v>1052</v>
       </c>
@@ -15379,7 +15532,7 @@
       <c r="J196" s="3"/>
       <c r="K196" s="3"/>
     </row>
-    <row r="197" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="3" t="s">
         <v>1058</v>
       </c>
@@ -15406,7 +15559,7 @@
       <c r="J197" s="3"/>
       <c r="K197" s="3"/>
     </row>
-    <row r="198" spans="1:11" ht="304.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:11" ht="304.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" s="3" t="s">
         <v>1063</v>
       </c>
@@ -15433,7 +15586,7 @@
       <c r="J198" s="3"/>
       <c r="K198" s="3"/>
     </row>
-    <row r="199" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="3" t="s">
         <v>1068</v>
       </c>
@@ -15460,7 +15613,7 @@
       <c r="J199" s="3"/>
       <c r="K199" s="3"/>
     </row>
-    <row r="200" spans="1:11" ht="115.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:11" ht="116" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="3" t="s">
         <v>1074</v>
       </c>
@@ -15487,7 +15640,7 @@
       <c r="J200" s="3"/>
       <c r="K200" s="3"/>
     </row>
-    <row r="201" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="3" t="s">
         <v>1079</v>
       </c>
@@ -15512,7 +15665,7 @@
       <c r="J201" s="3"/>
       <c r="K201" s="3"/>
     </row>
-    <row r="202" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="3" t="s">
         <v>1083</v>
       </c>
@@ -15537,7 +15690,7 @@
       <c r="J202" s="3"/>
       <c r="K202" s="3"/>
     </row>
-    <row r="203" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" s="3" t="s">
         <v>1088</v>
       </c>
@@ -15564,7 +15717,7 @@
       <c r="J203" s="3"/>
       <c r="K203" s="3"/>
     </row>
-    <row r="204" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" s="3" t="s">
         <v>1093</v>
       </c>
@@ -15591,7 +15744,7 @@
       <c r="J204" s="3"/>
       <c r="K204" s="3"/>
     </row>
-    <row r="205" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A205" s="3" t="s">
         <v>1099</v>
       </c>
@@ -15618,7 +15771,7 @@
       <c r="J205" s="3"/>
       <c r="K205" s="3"/>
     </row>
-    <row r="206" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" s="3" t="s">
         <v>1104</v>
       </c>
@@ -15645,7 +15798,7 @@
       <c r="J206" s="3"/>
       <c r="K206" s="3"/>
     </row>
-    <row r="207" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207" s="3" t="s">
         <v>1109</v>
       </c>
@@ -15672,7 +15825,7 @@
       <c r="J207" s="3"/>
       <c r="K207" s="3"/>
     </row>
-    <row r="208" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" s="3" t="s">
         <v>1115</v>
       </c>
@@ -15699,7 +15852,7 @@
       <c r="J208" s="3"/>
       <c r="K208" s="3"/>
     </row>
-    <row r="209" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209" s="3" t="s">
         <v>1120</v>
       </c>
@@ -15726,7 +15879,7 @@
       <c r="J209" s="3"/>
       <c r="K209" s="3"/>
     </row>
-    <row r="210" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210" s="3" t="s">
         <v>1125</v>
       </c>
@@ -15753,7 +15906,7 @@
       <c r="J210" s="3"/>
       <c r="K210" s="3"/>
     </row>
-    <row r="211" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211" s="3" t="s">
         <v>1131</v>
       </c>
@@ -15780,7 +15933,7 @@
       <c r="J211" s="3"/>
       <c r="K211" s="3"/>
     </row>
-    <row r="212" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" s="3" t="s">
         <v>1137</v>
       </c>
@@ -15807,7 +15960,7 @@
       <c r="J212" s="3"/>
       <c r="K212" s="3"/>
     </row>
-    <row r="213" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213" s="3" t="s">
         <v>1142</v>
       </c>
@@ -15834,7 +15987,7 @@
       <c r="J213" s="3"/>
       <c r="K213" s="3"/>
     </row>
-    <row r="214" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A214" s="3" t="s">
         <v>1148</v>
       </c>
@@ -15861,7 +16014,7 @@
       <c r="J214" s="3"/>
       <c r="K214" s="3"/>
     </row>
-    <row r="215" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A215" s="3" t="s">
         <v>1154</v>
       </c>
@@ -15888,7 +16041,7 @@
       <c r="J215" s="3"/>
       <c r="K215" s="3"/>
     </row>
-    <row r="216" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A216" s="3" t="s">
         <v>1159</v>
       </c>
@@ -15915,7 +16068,7 @@
       <c r="J216" s="3"/>
       <c r="K216" s="3"/>
     </row>
-    <row r="217" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217" s="3" t="s">
         <v>1165</v>
       </c>
@@ -15940,7 +16093,7 @@
       <c r="J217" s="3"/>
       <c r="K217" s="3"/>
     </row>
-    <row r="218" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A218" s="3" t="s">
         <v>1170</v>
       </c>
@@ -15967,7 +16120,7 @@
       <c r="J218" s="3"/>
       <c r="K218" s="3"/>
     </row>
-    <row r="219" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219" s="3" t="s">
         <v>1176</v>
       </c>
@@ -15994,7 +16147,7 @@
       <c r="J219" s="3"/>
       <c r="K219" s="3"/>
     </row>
-    <row r="220" spans="1:11" ht="275.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:11" ht="275.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220" s="3" t="s">
         <v>1182</v>
       </c>
@@ -16021,7 +16174,7 @@
       <c r="J220" s="3"/>
       <c r="K220" s="3"/>
     </row>
-    <row r="221" spans="1:11" ht="304.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:11" ht="304.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" s="3" t="s">
         <v>1187</v>
       </c>
@@ -16048,7 +16201,7 @@
       <c r="J221" s="3"/>
       <c r="K221" s="3"/>
     </row>
-    <row r="222" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A222" s="3" t="s">
         <v>1193</v>
       </c>
@@ -16073,7 +16226,7 @@
       <c r="J222" s="3"/>
       <c r="K222" s="3"/>
     </row>
-    <row r="223" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A223" s="3" t="s">
         <v>1198</v>
       </c>
@@ -16100,7 +16253,7 @@
       <c r="J223" s="3"/>
       <c r="K223" s="3"/>
     </row>
-    <row r="224" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224" s="3" t="s">
         <v>1204</v>
       </c>
@@ -16127,7 +16280,7 @@
       <c r="J224" s="3"/>
       <c r="K224" s="3"/>
     </row>
-    <row r="225" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" s="3" t="s">
         <v>1210</v>
       </c>
@@ -16152,7 +16305,7 @@
       <c r="J225" s="3"/>
       <c r="K225" s="3"/>
     </row>
-    <row r="226" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" s="3" t="s">
         <v>1215</v>
       </c>
@@ -16179,7 +16332,7 @@
       <c r="J226" s="3"/>
       <c r="K226" s="3"/>
     </row>
-    <row r="227" spans="1:11" ht="87" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:11" ht="87" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A227" s="3" t="s">
         <v>1220</v>
       </c>
@@ -16206,7 +16359,7 @@
       <c r="J227" s="3"/>
       <c r="K227" s="3"/>
     </row>
-    <row r="228" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" s="3" t="s">
         <v>1226</v>
       </c>
@@ -16231,7 +16384,7 @@
       <c r="J228" s="3"/>
       <c r="K228" s="3"/>
     </row>
-    <row r="229" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229" s="3" t="s">
         <v>1231</v>
       </c>
@@ -16258,7 +16411,7 @@
       <c r="J229" s="3"/>
       <c r="K229" s="3"/>
     </row>
-    <row r="230" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A230" s="3" t="s">
         <v>1237</v>
       </c>
@@ -16285,7 +16438,7 @@
       <c r="J230" s="3"/>
       <c r="K230" s="3"/>
     </row>
-    <row r="231" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" s="3" t="s">
         <v>1242</v>
       </c>
@@ -16312,7 +16465,7 @@
       <c r="J231" s="3"/>
       <c r="K231" s="3"/>
     </row>
-    <row r="232" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A232" s="3" t="s">
         <v>1247</v>
       </c>
@@ -16339,7 +16492,7 @@
       <c r="J232" s="3"/>
       <c r="K232" s="3"/>
     </row>
-    <row r="233" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A233" s="3" t="s">
         <v>1252</v>
       </c>
@@ -16366,7 +16519,7 @@
       <c r="J233" s="3"/>
       <c r="K233" s="3"/>
     </row>
-    <row r="234" spans="1:11" ht="333.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:11" ht="333.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A234" s="3" t="s">
         <v>1257</v>
       </c>
@@ -16393,7 +16546,7 @@
       <c r="J234" s="3"/>
       <c r="K234" s="3"/>
     </row>
-    <row r="235" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A235" s="3" t="s">
         <v>1263</v>
       </c>
@@ -16420,7 +16573,7 @@
       <c r="J235" s="3"/>
       <c r="K235" s="3"/>
     </row>
-    <row r="236" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A236" s="3" t="s">
         <v>1269</v>
       </c>
@@ -16447,7 +16600,7 @@
       <c r="J236" s="3"/>
       <c r="K236" s="3"/>
     </row>
-    <row r="237" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A237" s="3" t="s">
         <v>1275</v>
       </c>
@@ -16474,7 +16627,7 @@
       <c r="J237" s="3"/>
       <c r="K237" s="3"/>
     </row>
-    <row r="238" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A238" s="3" t="s">
         <v>1280</v>
       </c>
@@ -16499,7 +16652,7 @@
       <c r="J238" s="3"/>
       <c r="K238" s="3"/>
     </row>
-    <row r="239" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239" s="3" t="s">
         <v>1285</v>
       </c>
@@ -16526,7 +16679,7 @@
       <c r="J239" s="3"/>
       <c r="K239" s="3"/>
     </row>
-    <row r="240" spans="1:11" ht="319.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:11" ht="319" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A240" s="3" t="s">
         <v>1291</v>
       </c>
@@ -16553,7 +16706,7 @@
       <c r="J240" s="3"/>
       <c r="K240" s="3"/>
     </row>
-    <row r="241" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A241" s="3" t="s">
         <v>1296</v>
       </c>
@@ -16578,7 +16731,7 @@
       <c r="J241" s="3"/>
       <c r="K241" s="3"/>
     </row>
-    <row r="242" spans="1:11" ht="101.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:11" ht="101.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A242" s="3" t="s">
         <v>1300</v>
       </c>
@@ -16605,7 +16758,7 @@
       <c r="J242" s="3"/>
       <c r="K242" s="3"/>
     </row>
-    <row r="243" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A243" s="3" t="s">
         <v>1306</v>
       </c>
@@ -16632,7 +16785,7 @@
       <c r="J243" s="3"/>
       <c r="K243" s="3"/>
     </row>
-    <row r="244" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A244" s="3" t="s">
         <v>1311</v>
       </c>
@@ -16659,7 +16812,7 @@
       <c r="J244" s="3"/>
       <c r="K244" s="3"/>
     </row>
-    <row r="245" spans="1:11" ht="333.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:11" ht="333.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A245" s="3" t="s">
         <v>1316</v>
       </c>
@@ -16686,7 +16839,7 @@
       <c r="J245" s="3"/>
       <c r="K245" s="3"/>
     </row>
-    <row r="246" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A246" s="3" t="s">
         <v>1322</v>
       </c>
@@ -16711,7 +16864,7 @@
       <c r="J246" s="3"/>
       <c r="K246" s="3"/>
     </row>
-    <row r="247" spans="1:11" ht="275.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:11" ht="275.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A247" s="3" t="s">
         <v>1326</v>
       </c>
@@ -16738,7 +16891,7 @@
       <c r="J247" s="3"/>
       <c r="K247" s="3"/>
     </row>
-    <row r="248" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A248" s="3" t="s">
         <v>1332</v>
       </c>
@@ -16765,7 +16918,7 @@
       <c r="J248" s="3"/>
       <c r="K248" s="3"/>
     </row>
-    <row r="249" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A249" s="3" t="s">
         <v>1337</v>
       </c>
@@ -16792,7 +16945,7 @@
       <c r="J249" s="3"/>
       <c r="K249" s="3"/>
     </row>
-    <row r="250" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A250" s="3" t="s">
         <v>1342</v>
       </c>
@@ -16819,7 +16972,7 @@
       <c r="J250" s="3"/>
       <c r="K250" s="3"/>
     </row>
-    <row r="251" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A251" s="3" t="s">
         <v>1347</v>
       </c>
@@ -16846,7 +16999,7 @@
       <c r="J251" s="3"/>
       <c r="K251" s="3"/>
     </row>
-    <row r="252" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252" s="3" t="s">
         <v>1352</v>
       </c>
@@ -16871,7 +17024,7 @@
       <c r="J252" s="3"/>
       <c r="K252" s="3"/>
     </row>
-    <row r="253" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A253" s="3" t="s">
         <v>1357</v>
       </c>
@@ -16898,7 +17051,7 @@
       <c r="J253" s="3"/>
       <c r="K253" s="3"/>
     </row>
-    <row r="254" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A254" s="3" t="s">
         <v>1362</v>
       </c>
@@ -16925,7 +17078,7 @@
       <c r="J254" s="3"/>
       <c r="K254" s="3"/>
     </row>
-    <row r="255" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A255" s="3" t="s">
         <v>1367</v>
       </c>
@@ -16952,7 +17105,7 @@
       <c r="J255" s="3"/>
       <c r="K255" s="3"/>
     </row>
-    <row r="256" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A256" s="3" t="s">
         <v>1373</v>
       </c>
@@ -16979,7 +17132,7 @@
       <c r="J256" s="3"/>
       <c r="K256" s="3"/>
     </row>
-    <row r="257" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A257" s="3" t="s">
         <v>1378</v>
       </c>
@@ -17006,7 +17159,7 @@
       <c r="J257" s="3"/>
       <c r="K257" s="3"/>
     </row>
-    <row r="258" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A258" s="3" t="s">
         <v>1384</v>
       </c>
@@ -17033,7 +17186,7 @@
       <c r="J258" s="3"/>
       <c r="K258" s="3"/>
     </row>
-    <row r="259" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A259" s="3" t="s">
         <v>1389</v>
       </c>
@@ -17060,7 +17213,7 @@
       <c r="J259" s="3"/>
       <c r="K259" s="3"/>
     </row>
-    <row r="260" spans="1:11" ht="275.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:11" ht="275.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A260" s="3" t="s">
         <v>1394</v>
       </c>
@@ -17087,7 +17240,7 @@
       <c r="J260" s="3"/>
       <c r="K260" s="3"/>
     </row>
-    <row r="261" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A261" s="3" t="s">
         <v>1399</v>
       </c>
@@ -17114,7 +17267,7 @@
       <c r="J261" s="3"/>
       <c r="K261" s="3"/>
     </row>
-    <row r="262" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A262" s="3" t="s">
         <v>1404</v>
       </c>
@@ -17139,7 +17292,7 @@
       <c r="J262" s="3"/>
       <c r="K262" s="3"/>
     </row>
-    <row r="263" spans="1:11" ht="115.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:11" ht="116" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A263" s="3" t="s">
         <v>1408</v>
       </c>
@@ -17164,7 +17317,7 @@
       <c r="J263" s="3"/>
       <c r="K263" s="3"/>
     </row>
-    <row r="264" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A264" s="3" t="s">
         <v>1412</v>
       </c>
@@ -17191,7 +17344,7 @@
       <c r="J264" s="3"/>
       <c r="K264" s="3"/>
     </row>
-    <row r="265" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A265" s="3" t="s">
         <v>1418</v>
       </c>
@@ -17218,7 +17371,7 @@
       <c r="J265" s="3"/>
       <c r="K265" s="3"/>
     </row>
-    <row r="266" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A266" s="3" t="s">
         <v>1423</v>
       </c>
@@ -17245,7 +17398,7 @@
       <c r="J266" s="3"/>
       <c r="K266" s="3"/>
     </row>
-    <row r="267" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A267" s="3" t="s">
         <v>1429</v>
       </c>
@@ -17272,7 +17425,7 @@
       <c r="J267" s="3"/>
       <c r="K267" s="3"/>
     </row>
-    <row r="268" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A268" s="3" t="s">
         <v>1435</v>
       </c>
@@ -17299,7 +17452,7 @@
       <c r="J268" s="3"/>
       <c r="K268" s="3"/>
     </row>
-    <row r="269" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A269" s="3" t="s">
         <v>1440</v>
       </c>
@@ -17324,7 +17477,7 @@
       <c r="J269" s="3"/>
       <c r="K269" s="3"/>
     </row>
-    <row r="270" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A270" s="3" t="s">
         <v>1445</v>
       </c>
@@ -17351,7 +17504,7 @@
       <c r="J270" s="3"/>
       <c r="K270" s="3"/>
     </row>
-    <row r="271" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A271" s="3" t="s">
         <v>1451</v>
       </c>
@@ -17378,7 +17531,7 @@
       <c r="J271" s="3"/>
       <c r="K271" s="3"/>
     </row>
-    <row r="272" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A272" s="3" t="s">
         <v>1457</v>
       </c>
@@ -17405,7 +17558,7 @@
       <c r="J272" s="3"/>
       <c r="K272" s="3"/>
     </row>
-    <row r="273" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A273" s="3" t="s">
         <v>1462</v>
       </c>
@@ -17432,7 +17585,7 @@
       <c r="J273" s="3"/>
       <c r="K273" s="3"/>
     </row>
-    <row r="274" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A274" s="3" t="s">
         <v>1467</v>
       </c>
@@ -17459,7 +17612,7 @@
       <c r="J274" s="3"/>
       <c r="K274" s="3"/>
     </row>
-    <row r="275" spans="1:11" ht="348" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:11" ht="348" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A275" s="3" t="s">
         <v>1473</v>
       </c>
@@ -17482,7 +17635,7 @@
       <c r="J275" s="3"/>
       <c r="K275" s="3"/>
     </row>
-    <row r="276" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A276" s="3" t="s">
         <v>1477</v>
       </c>
@@ -17509,7 +17662,7 @@
       <c r="J276" s="3"/>
       <c r="K276" s="3"/>
     </row>
-    <row r="277" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A277" s="3" t="s">
         <v>1483</v>
       </c>
@@ -17536,7 +17689,7 @@
       <c r="J277" s="3"/>
       <c r="K277" s="3"/>
     </row>
-    <row r="278" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A278" s="3" t="s">
         <v>1488</v>
       </c>
@@ -17563,7 +17716,7 @@
       <c r="J278" s="3"/>
       <c r="K278" s="3"/>
     </row>
-    <row r="279" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A279" s="3" t="s">
         <v>1494</v>
       </c>
@@ -17588,7 +17741,7 @@
       <c r="J279" s="3"/>
       <c r="K279" s="3"/>
     </row>
-    <row r="280" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A280" s="3" t="s">
         <v>1498</v>
       </c>
@@ -17615,7 +17768,7 @@
       <c r="J280" s="3"/>
       <c r="K280" s="3"/>
     </row>
-    <row r="281" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A281" s="3" t="s">
         <v>1504</v>
       </c>
@@ -17642,7 +17795,7 @@
       <c r="J281" s="3"/>
       <c r="K281" s="3"/>
     </row>
-    <row r="282" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A282" s="3" t="s">
         <v>1509</v>
       </c>
@@ -17669,7 +17822,7 @@
       <c r="J282" s="3"/>
       <c r="K282" s="3"/>
     </row>
-    <row r="283" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A283" s="3" t="s">
         <v>1514</v>
       </c>
@@ -17696,7 +17849,7 @@
       <c r="J283" s="3"/>
       <c r="K283" s="3"/>
     </row>
-    <row r="284" spans="1:11" ht="289.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:11" ht="290" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A284" s="3" t="s">
         <v>1519</v>
       </c>
@@ -17723,7 +17876,7 @@
       <c r="J284" s="3"/>
       <c r="K284" s="3"/>
     </row>
-    <row r="285" spans="1:11" ht="275.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:11" ht="275.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A285" s="3" t="s">
         <v>1524</v>
       </c>
@@ -17750,7 +17903,7 @@
       <c r="J285" s="3"/>
       <c r="K285" s="3"/>
     </row>
-    <row r="286" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A286" s="3" t="s">
         <v>1529</v>
       </c>
@@ -17777,7 +17930,7 @@
       <c r="J286" s="3"/>
       <c r="K286" s="3"/>
     </row>
-    <row r="287" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A287" s="3" t="s">
         <v>1535</v>
       </c>
@@ -17804,7 +17957,7 @@
       <c r="J287" s="3"/>
       <c r="K287" s="3"/>
     </row>
-    <row r="288" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A288" s="3" t="s">
         <v>1541</v>
       </c>
@@ -17831,7 +17984,7 @@
       <c r="J288" s="3"/>
       <c r="K288" s="3"/>
     </row>
-    <row r="289" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A289" s="3" t="s">
         <v>1546</v>
       </c>
@@ -17858,7 +18011,7 @@
       <c r="J289" s="3"/>
       <c r="K289" s="3"/>
     </row>
-    <row r="290" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A290" s="3" t="s">
         <v>1551</v>
       </c>
@@ -17883,7 +18036,7 @@
       <c r="J290" s="3"/>
       <c r="K290" s="3"/>
     </row>
-    <row r="291" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A291" s="3" t="s">
         <v>1556</v>
       </c>
@@ -17910,7 +18063,7 @@
       <c r="J291" s="3"/>
       <c r="K291" s="3"/>
     </row>
-    <row r="292" spans="1:11" ht="289.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:11" ht="290" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A292" s="3" t="s">
         <v>1562</v>
       </c>
@@ -17937,7 +18090,7 @@
       <c r="J292" s="3"/>
       <c r="K292" s="3"/>
     </row>
-    <row r="293" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A293" s="3" t="s">
         <v>1568</v>
       </c>
@@ -17964,7 +18117,7 @@
       <c r="J293" s="3"/>
       <c r="K293" s="3"/>
     </row>
-    <row r="294" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A294" s="3" t="s">
         <v>1573</v>
       </c>
@@ -17991,7 +18144,7 @@
       <c r="J294" s="3"/>
       <c r="K294" s="3"/>
     </row>
-    <row r="295" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A295" s="3" t="s">
         <v>1579</v>
       </c>
@@ -18018,7 +18171,7 @@
       <c r="J295" s="3"/>
       <c r="K295" s="3"/>
     </row>
-    <row r="296" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A296" s="3" t="s">
         <v>1585</v>
       </c>
@@ -18045,7 +18198,7 @@
       <c r="J296" s="3"/>
       <c r="K296" s="3"/>
     </row>
-    <row r="297" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A297" s="3" t="s">
         <v>1590</v>
       </c>
@@ -18072,7 +18225,7 @@
       <c r="J297" s="3"/>
       <c r="K297" s="3"/>
     </row>
-    <row r="298" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A298" s="3" t="s">
         <v>1596</v>
       </c>
@@ -18099,7 +18252,7 @@
       <c r="J298" s="3"/>
       <c r="K298" s="3"/>
     </row>
-    <row r="299" spans="1:11" ht="406.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:11" ht="406" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A299" s="3" t="s">
         <v>1601</v>
       </c>
@@ -18126,7 +18279,7 @@
       <c r="J299" s="3"/>
       <c r="K299" s="3"/>
     </row>
-    <row r="300" spans="1:11" ht="101.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:11" ht="101.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A300" s="3" t="s">
         <v>1606</v>
       </c>
@@ -18153,7 +18306,7 @@
       <c r="J300" s="3"/>
       <c r="K300" s="3"/>
     </row>
-    <row r="301" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A301" s="3" t="s">
         <v>1611</v>
       </c>
@@ -18180,7 +18333,7 @@
       <c r="J301" s="3"/>
       <c r="K301" s="3"/>
     </row>
-    <row r="302" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A302" s="3" t="s">
         <v>1616</v>
       </c>
@@ -18207,7 +18360,7 @@
       <c r="J302" s="3"/>
       <c r="K302" s="3"/>
     </row>
-    <row r="303" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A303" s="3" t="s">
         <v>1621</v>
       </c>
@@ -18234,7 +18387,7 @@
       <c r="J303" s="3"/>
       <c r="K303" s="3"/>
     </row>
-    <row r="304" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A304" s="3" t="s">
         <v>1626</v>
       </c>
@@ -18261,7 +18414,7 @@
       <c r="J304" s="3"/>
       <c r="K304" s="3"/>
     </row>
-    <row r="305" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A305" s="3" t="s">
         <v>1631</v>
       </c>
@@ -18288,7 +18441,7 @@
       <c r="J305" s="3"/>
       <c r="K305" s="3"/>
     </row>
-    <row r="306" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A306" s="3" t="s">
         <v>1636</v>
       </c>
@@ -18315,7 +18468,7 @@
       <c r="J306" s="3"/>
       <c r="K306" s="3"/>
     </row>
-    <row r="307" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A307" s="3" t="s">
         <v>1641</v>
       </c>
@@ -18342,7 +18495,7 @@
       <c r="J307" s="3"/>
       <c r="K307" s="3"/>
     </row>
-    <row r="308" spans="1:11" ht="409.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:11" ht="409.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A308" s="3" t="s">
         <v>1646</v>
       </c>
@@ -18365,7 +18518,7 @@
       <c r="J308" s="3"/>
       <c r="K308" s="3"/>
     </row>
-    <row r="309" spans="1:11" ht="275.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:11" ht="275.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A309" s="3" t="s">
         <v>1650</v>
       </c>
@@ -18392,7 +18545,7 @@
       <c r="J309" s="3"/>
       <c r="K309" s="3"/>
     </row>
-    <row r="310" spans="1:11" ht="304.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:11" ht="304.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A310" s="3" t="s">
         <v>1656</v>
       </c>
@@ -18419,7 +18572,7 @@
       <c r="J310" s="3"/>
       <c r="K310" s="3"/>
     </row>
-    <row r="311" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A311" s="3" t="s">
         <v>1662</v>
       </c>
@@ -18444,7 +18597,7 @@
       <c r="J311" s="3"/>
       <c r="K311" s="3"/>
     </row>
-    <row r="312" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A312" s="3" t="s">
         <v>1666</v>
       </c>
@@ -18471,7 +18624,7 @@
       <c r="J312" s="3"/>
       <c r="K312" s="3"/>
     </row>
-    <row r="313" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A313" s="3" t="s">
         <v>1672</v>
       </c>
@@ -18498,7 +18651,7 @@
       <c r="J313" s="3"/>
       <c r="K313" s="3"/>
     </row>
-    <row r="314" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A314" s="3" t="s">
         <v>1677</v>
       </c>
@@ -18525,7 +18678,7 @@
       <c r="J314" s="3"/>
       <c r="K314" s="3"/>
     </row>
-    <row r="315" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A315" s="3" t="s">
         <v>1683</v>
       </c>
@@ -18552,7 +18705,7 @@
       <c r="J315" s="3"/>
       <c r="K315" s="3"/>
     </row>
-    <row r="316" spans="1:11" ht="289.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:11" ht="290" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A316" s="3" t="s">
         <v>1688</v>
       </c>
@@ -18579,7 +18732,7 @@
       <c r="J316" s="3"/>
       <c r="K316" s="3"/>
     </row>
-    <row r="317" spans="1:11" ht="289.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:11" ht="290" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A317" s="3" t="s">
         <v>1693</v>
       </c>
@@ -18606,7 +18759,7 @@
       <c r="J317" s="3"/>
       <c r="K317" s="3"/>
     </row>
-    <row r="318" spans="1:11" ht="275.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:11" ht="275.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A318" s="3" t="s">
         <v>1699</v>
       </c>
@@ -18633,7 +18786,7 @@
       <c r="J318" s="3"/>
       <c r="K318" s="3"/>
     </row>
-    <row r="319" spans="1:11" ht="115.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:11" ht="116" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A319" s="3" t="s">
         <v>1704</v>
       </c>
@@ -18658,7 +18811,7 @@
       <c r="J319" s="3"/>
       <c r="K319" s="3"/>
     </row>
-    <row r="320" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A320" s="3" t="s">
         <v>1709</v>
       </c>
@@ -18685,7 +18838,7 @@
       <c r="J320" s="3"/>
       <c r="K320" s="3"/>
     </row>
-    <row r="321" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A321" s="3" t="s">
         <v>1715</v>
       </c>
@@ -18712,7 +18865,7 @@
       <c r="J321" s="3"/>
       <c r="K321" s="3"/>
     </row>
-    <row r="322" spans="1:11" ht="304.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:11" ht="304.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A322" s="3" t="s">
         <v>1720</v>
       </c>
@@ -18739,7 +18892,7 @@
       <c r="J322" s="3"/>
       <c r="K322" s="3"/>
     </row>
-    <row r="323" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A323" s="3" t="s">
         <v>1726</v>
       </c>
@@ -18764,7 +18917,7 @@
       <c r="J323" s="3"/>
       <c r="K323" s="3"/>
     </row>
-    <row r="324" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A324" s="3" t="s">
         <v>1730</v>
       </c>
@@ -18791,7 +18944,7 @@
       <c r="J324" s="3"/>
       <c r="K324" s="3"/>
     </row>
-    <row r="325" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A325" s="3" t="s">
         <v>1735</v>
       </c>
@@ -18818,7 +18971,7 @@
       <c r="J325" s="3"/>
       <c r="K325" s="3"/>
     </row>
-    <row r="326" spans="1:11" ht="289.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:11" ht="290" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A326" s="3" t="s">
         <v>1740</v>
       </c>
@@ -18843,7 +18996,7 @@
       <c r="J326" s="3"/>
       <c r="K326" s="3"/>
     </row>
-    <row r="327" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A327" s="3" t="s">
         <v>1744</v>
       </c>
@@ -18868,7 +19021,7 @@
       <c r="J327" s="3"/>
       <c r="K327" s="3"/>
     </row>
-    <row r="328" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A328" s="3" t="s">
         <v>1748</v>
       </c>
@@ -18895,7 +19048,7 @@
       <c r="J328" s="3"/>
       <c r="K328" s="3"/>
     </row>
-    <row r="329" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A329" s="3" t="s">
         <v>1753</v>
       </c>
@@ -18922,7 +19075,7 @@
       <c r="J329" s="3"/>
       <c r="K329" s="3"/>
     </row>
-    <row r="330" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A330" s="3" t="s">
         <v>1758</v>
       </c>
@@ -18949,7 +19102,7 @@
       <c r="J330" s="3"/>
       <c r="K330" s="3"/>
     </row>
-    <row r="331" spans="1:11" ht="406.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:11" ht="406" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A331" s="3" t="s">
         <v>1763</v>
       </c>
@@ -18974,7 +19127,7 @@
       <c r="J331" s="3"/>
       <c r="K331" s="3"/>
     </row>
-    <row r="332" spans="1:11" ht="333.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:11" ht="333.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A332" s="3" t="s">
         <v>1767</v>
       </c>
@@ -19001,7 +19154,7 @@
       <c r="J332" s="3"/>
       <c r="K332" s="3"/>
     </row>
-    <row r="333" spans="1:11" ht="115.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:11" ht="116" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A333" s="3" t="s">
         <v>1772</v>
       </c>
@@ -19026,7 +19179,7 @@
       <c r="J333" s="3"/>
       <c r="K333" s="3"/>
     </row>
-    <row r="334" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A334" s="3" t="s">
         <v>1776</v>
       </c>
@@ -19053,7 +19206,7 @@
       <c r="J334" s="3"/>
       <c r="K334" s="3"/>
     </row>
-    <row r="335" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A335" s="3" t="s">
         <v>1781</v>
       </c>
@@ -19080,7 +19233,7 @@
       <c r="J335" s="3"/>
       <c r="K335" s="3"/>
     </row>
-    <row r="336" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A336" s="3" t="s">
         <v>1787</v>
       </c>
@@ -19107,7 +19260,7 @@
       <c r="J336" s="3"/>
       <c r="K336" s="3"/>
     </row>
-    <row r="337" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A337" s="3" t="s">
         <v>1793</v>
       </c>
@@ -19134,7 +19287,7 @@
       <c r="J337" s="3"/>
       <c r="K337" s="3"/>
     </row>
-    <row r="338" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A338" s="3" t="s">
         <v>1799</v>
       </c>
@@ -19159,7 +19312,7 @@
       <c r="J338" s="3"/>
       <c r="K338" s="3"/>
     </row>
-    <row r="339" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A339" s="3" t="s">
         <v>1803</v>
       </c>
@@ -19184,7 +19337,7 @@
       <c r="J339" s="3"/>
       <c r="K339" s="3"/>
     </row>
-    <row r="340" spans="1:11" ht="289.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:11" ht="290" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A340" s="3" t="s">
         <v>1807</v>
       </c>
@@ -19211,7 +19364,7 @@
       <c r="J340" s="3"/>
       <c r="K340" s="3"/>
     </row>
-    <row r="341" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A341" s="3" t="s">
         <v>1812</v>
       </c>
@@ -19238,7 +19391,7 @@
       <c r="J341" s="3"/>
       <c r="K341" s="3"/>
     </row>
-    <row r="342" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A342" s="3" t="s">
         <v>1818</v>
       </c>
@@ -19265,7 +19418,7 @@
       <c r="J342" s="3"/>
       <c r="K342" s="3"/>
     </row>
-    <row r="343" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A343" s="3" t="s">
         <v>1823</v>
       </c>
@@ -19292,7 +19445,7 @@
       <c r="J343" s="3"/>
       <c r="K343" s="3"/>
     </row>
-    <row r="344" spans="1:11" ht="391.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:11" ht="391.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A344" s="3" t="s">
         <v>1829</v>
       </c>
@@ -19319,7 +19472,7 @@
       <c r="J344" s="3"/>
       <c r="K344" s="3"/>
     </row>
-    <row r="345" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A345" s="3" t="s">
         <v>1835</v>
       </c>
@@ -19346,7 +19499,7 @@
       <c r="J345" s="3"/>
       <c r="K345" s="3"/>
     </row>
-    <row r="346" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A346" s="3" t="s">
         <v>1840</v>
       </c>
@@ -19373,7 +19526,7 @@
       <c r="J346" s="3"/>
       <c r="K346" s="3"/>
     </row>
-    <row r="347" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A347" s="3" t="s">
         <v>1845</v>
       </c>
@@ -19400,7 +19553,7 @@
       <c r="J347" s="3"/>
       <c r="K347" s="3"/>
     </row>
-    <row r="348" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A348" s="3" t="s">
         <v>1850</v>
       </c>
@@ -19427,7 +19580,7 @@
       <c r="J348" s="3"/>
       <c r="K348" s="3"/>
     </row>
-    <row r="349" spans="1:11" ht="115.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:11" ht="116" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A349" s="3" t="s">
         <v>1856</v>
       </c>
@@ -19454,7 +19607,7 @@
       <c r="J349" s="3"/>
       <c r="K349" s="3"/>
     </row>
-    <row r="350" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A350" s="3" t="s">
         <v>1862</v>
       </c>
@@ -19479,7 +19632,7 @@
       <c r="J350" s="3"/>
       <c r="K350" s="3"/>
     </row>
-    <row r="351" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A351" s="3" t="s">
         <v>1866</v>
       </c>
@@ -19506,7 +19659,7 @@
       <c r="J351" s="3"/>
       <c r="K351" s="3"/>
     </row>
-    <row r="352" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A352" s="3" t="s">
         <v>1872</v>
       </c>
@@ -19533,7 +19686,7 @@
       <c r="J352" s="3"/>
       <c r="K352" s="3"/>
     </row>
-    <row r="353" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A353" s="3" t="s">
         <v>1878</v>
       </c>
@@ -19560,7 +19713,7 @@
       <c r="J353" s="3"/>
       <c r="K353" s="3"/>
     </row>
-    <row r="354" spans="1:11" ht="275.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:11" ht="275.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A354" s="3" t="s">
         <v>1883</v>
       </c>
@@ -19585,7 +19738,7 @@
       <c r="J354" s="3"/>
       <c r="K354" s="3"/>
     </row>
-    <row r="355" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A355" s="3" t="s">
         <v>1887</v>
       </c>
@@ -19612,7 +19765,7 @@
       <c r="J355" s="3"/>
       <c r="K355" s="3"/>
     </row>
-    <row r="356" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A356" s="3" t="s">
         <v>1893</v>
       </c>
@@ -19639,7 +19792,7 @@
       <c r="J356" s="3"/>
       <c r="K356" s="3"/>
     </row>
-    <row r="357" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A357" s="3" t="s">
         <v>1899</v>
       </c>
@@ -19664,7 +19817,7 @@
       <c r="J357" s="3"/>
       <c r="K357" s="3"/>
     </row>
-    <row r="358" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A358" s="3" t="s">
         <v>1904</v>
       </c>
@@ -19687,7 +19840,7 @@
       <c r="J358" s="3"/>
       <c r="K358" s="3"/>
     </row>
-    <row r="359" spans="1:11" ht="289.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:11" ht="290" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A359" s="3" t="s">
         <v>1908</v>
       </c>
@@ -19714,7 +19867,7 @@
       <c r="J359" s="3"/>
       <c r="K359" s="3"/>
     </row>
-    <row r="360" spans="1:11" ht="115.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:11" ht="116" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A360" s="3" t="s">
         <v>1914</v>
       </c>
@@ -19741,7 +19894,7 @@
       <c r="J360" s="3"/>
       <c r="K360" s="3"/>
     </row>
-    <row r="361" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A361" s="3" t="s">
         <v>1920</v>
       </c>
@@ -19768,7 +19921,7 @@
       <c r="J361" s="3"/>
       <c r="K361" s="3"/>
     </row>
-    <row r="362" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A362" s="3" t="s">
         <v>1925</v>
       </c>
@@ -19793,7 +19946,7 @@
       <c r="J362" s="3"/>
       <c r="K362" s="3"/>
     </row>
-    <row r="363" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A363" s="3" t="s">
         <v>1929</v>
       </c>
@@ -19820,7 +19973,7 @@
       <c r="J363" s="3"/>
       <c r="K363" s="3"/>
     </row>
-    <row r="364" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A364" s="3" t="s">
         <v>1935</v>
       </c>
@@ -19847,7 +20000,7 @@
       <c r="J364" s="3"/>
       <c r="K364" s="3"/>
     </row>
-    <row r="365" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A365" s="3" t="s">
         <v>1940</v>
       </c>
@@ -19874,7 +20027,7 @@
       <c r="J365" s="3"/>
       <c r="K365" s="3"/>
     </row>
-    <row r="366" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A366" s="3" t="s">
         <v>1946</v>
       </c>
@@ -19901,7 +20054,7 @@
       <c r="J366" s="3"/>
       <c r="K366" s="3"/>
     </row>
-    <row r="367" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A367" s="3" t="s">
         <v>1951</v>
       </c>
@@ -19926,7 +20079,7 @@
       <c r="J367" s="3"/>
       <c r="K367" s="3"/>
     </row>
-    <row r="368" spans="1:11" ht="289.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:11" ht="290" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A368" s="3" t="s">
         <v>1955</v>
       </c>
@@ -19953,7 +20106,7 @@
       <c r="J368" s="3"/>
       <c r="K368" s="3"/>
     </row>
-    <row r="369" spans="1:11" ht="319.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:11" ht="319" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A369" s="3" t="s">
         <v>1960</v>
       </c>
@@ -19980,7 +20133,7 @@
       <c r="J369" s="3"/>
       <c r="K369" s="3"/>
     </row>
-    <row r="370" spans="1:11" ht="275.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:11" ht="275.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A370" s="3" t="s">
         <v>1965</v>
       </c>
@@ -20007,7 +20160,7 @@
       <c r="J370" s="3"/>
       <c r="K370" s="3"/>
     </row>
-    <row r="371" spans="1:11" ht="319.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:11" ht="319" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A371" s="3" t="s">
         <v>1970</v>
       </c>
@@ -20030,7 +20183,7 @@
       <c r="J371" s="3"/>
       <c r="K371" s="3"/>
     </row>
-    <row r="372" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A372" s="3" t="s">
         <v>1974</v>
       </c>
@@ -20057,7 +20210,7 @@
       <c r="J372" s="3"/>
       <c r="K372" s="3"/>
     </row>
-    <row r="373" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A373" s="3" t="s">
         <v>1979</v>
       </c>
@@ -20084,7 +20237,7 @@
       <c r="J373" s="3"/>
       <c r="K373" s="3"/>
     </row>
-    <row r="374" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A374" s="3" t="s">
         <v>1985</v>
       </c>
@@ -20111,7 +20264,7 @@
       <c r="J374" s="3"/>
       <c r="K374" s="3"/>
     </row>
-    <row r="375" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A375" s="3" t="s">
         <v>1990</v>
       </c>
@@ -20138,7 +20291,7 @@
       <c r="J375" s="3"/>
       <c r="K375" s="3"/>
     </row>
-    <row r="376" spans="1:11" ht="101.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:11" ht="101.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A376" s="3" t="s">
         <v>1995</v>
       </c>
@@ -20165,7 +20318,7 @@
       <c r="J376" s="3"/>
       <c r="K376" s="3"/>
     </row>
-    <row r="377" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A377" s="3" t="s">
         <v>2000</v>
       </c>
@@ -20192,7 +20345,7 @@
       <c r="J377" s="3"/>
       <c r="K377" s="3"/>
     </row>
-    <row r="378" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A378" s="3" t="s">
         <v>2005</v>
       </c>
@@ -20219,7 +20372,7 @@
       <c r="J378" s="3"/>
       <c r="K378" s="3"/>
     </row>
-    <row r="379" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A379" s="3" t="s">
         <v>2011</v>
       </c>
@@ -20246,7 +20399,7 @@
       <c r="J379" s="3"/>
       <c r="K379" s="3"/>
     </row>
-    <row r="380" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A380" s="3" t="s">
         <v>2016</v>
       </c>
@@ -20273,7 +20426,7 @@
       <c r="J380" s="3"/>
       <c r="K380" s="3"/>
     </row>
-    <row r="381" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A381" s="3" t="s">
         <v>2021</v>
       </c>
@@ -20300,7 +20453,7 @@
       <c r="J381" s="3"/>
       <c r="K381" s="3"/>
     </row>
-    <row r="382" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A382" s="3" t="s">
         <v>2027</v>
       </c>
@@ -20327,7 +20480,7 @@
       <c r="J382" s="3"/>
       <c r="K382" s="3"/>
     </row>
-    <row r="383" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A383" s="3" t="s">
         <v>2032</v>
       </c>
@@ -20354,7 +20507,7 @@
       <c r="J383" s="3"/>
       <c r="K383" s="3"/>
     </row>
-    <row r="384" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A384" s="3" t="s">
         <v>2038</v>
       </c>
@@ -20381,7 +20534,7 @@
       <c r="J384" s="3"/>
       <c r="K384" s="3"/>
     </row>
-    <row r="385" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A385" s="3" t="s">
         <v>2043</v>
       </c>
@@ -20408,7 +20561,7 @@
       <c r="J385" s="3"/>
       <c r="K385" s="3"/>
     </row>
-    <row r="386" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A386" s="3" t="s">
         <v>2048</v>
       </c>
@@ -20435,7 +20588,7 @@
       <c r="J386" s="3"/>
       <c r="K386" s="3"/>
     </row>
-    <row r="387" spans="1:11" ht="275.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:11" ht="275.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A387" s="3" t="s">
         <v>2054</v>
       </c>
@@ -20462,7 +20615,7 @@
       <c r="J387" s="3"/>
       <c r="K387" s="3"/>
     </row>
-    <row r="388" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A388" s="3" t="s">
         <v>2059</v>
       </c>
@@ -20489,7 +20642,7 @@
       <c r="J388" s="3"/>
       <c r="K388" s="3"/>
     </row>
-    <row r="389" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A389" s="3" t="s">
         <v>2064</v>
       </c>
@@ -20516,7 +20669,7 @@
       <c r="J389" s="3"/>
       <c r="K389" s="3"/>
     </row>
-    <row r="390" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A390" s="3" t="s">
         <v>2070</v>
       </c>
@@ -20543,7 +20696,7 @@
       <c r="J390" s="3"/>
       <c r="K390" s="3"/>
     </row>
-    <row r="391" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A391" s="3" t="s">
         <v>2075</v>
       </c>
@@ -20570,7 +20723,7 @@
       <c r="J391" s="3"/>
       <c r="K391" s="3"/>
     </row>
-    <row r="392" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A392" s="3" t="s">
         <v>2080</v>
       </c>
@@ -20597,7 +20750,7 @@
       <c r="J392" s="3"/>
       <c r="K392" s="3"/>
     </row>
-    <row r="393" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A393" s="3" t="s">
         <v>2085</v>
       </c>
@@ -20624,7 +20777,7 @@
       <c r="J393" s="3"/>
       <c r="K393" s="3"/>
     </row>
-    <row r="394" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A394" s="3" t="s">
         <v>2090</v>
       </c>
@@ -20651,7 +20804,7 @@
       <c r="J394" s="3"/>
       <c r="K394" s="3"/>
     </row>
-    <row r="395" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A395" s="3" t="s">
         <v>2095</v>
       </c>
@@ -20678,7 +20831,7 @@
       <c r="J395" s="3"/>
       <c r="K395" s="3"/>
     </row>
-    <row r="396" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A396" s="3" t="s">
         <v>2100</v>
       </c>
@@ -20705,7 +20858,7 @@
       <c r="J396" s="3"/>
       <c r="K396" s="3"/>
     </row>
-    <row r="397" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A397" s="3" t="s">
         <v>2105</v>
       </c>
@@ -20730,7 +20883,7 @@
       <c r="J397" s="3"/>
       <c r="K397" s="3"/>
     </row>
-    <row r="398" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A398" s="3" t="s">
         <v>2110</v>
       </c>
@@ -20757,7 +20910,7 @@
       <c r="J398" s="3"/>
       <c r="K398" s="3"/>
     </row>
-    <row r="399" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A399" s="3" t="s">
         <v>2115</v>
       </c>
@@ -20782,7 +20935,7 @@
       <c r="J399" s="3"/>
       <c r="K399" s="3"/>
     </row>
-    <row r="400" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A400" s="3" t="s">
         <v>2119</v>
       </c>
@@ -20809,7 +20962,7 @@
       <c r="J400" s="3"/>
       <c r="K400" s="3"/>
     </row>
-    <row r="401" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A401" s="3" t="s">
         <v>2124</v>
       </c>
@@ -20836,7 +20989,7 @@
       <c r="J401" s="3"/>
       <c r="K401" s="3"/>
     </row>
-    <row r="402" spans="1:11" ht="289.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:11" ht="290" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A402" s="3" t="s">
         <v>2129</v>
       </c>
@@ -20863,7 +21016,7 @@
       <c r="J402" s="3"/>
       <c r="K402" s="3"/>
     </row>
-    <row r="403" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A403" s="3" t="s">
         <v>2134</v>
       </c>
@@ -20888,7 +21041,7 @@
       <c r="J403" s="3"/>
       <c r="K403" s="3"/>
     </row>
-    <row r="404" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A404" s="3" t="s">
         <v>2138</v>
       </c>
@@ -20915,7 +21068,7 @@
       <c r="J404" s="3"/>
       <c r="K404" s="3"/>
     </row>
-    <row r="405" spans="1:11" ht="275.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:11" ht="275.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A405" s="3" t="s">
         <v>2143</v>
       </c>
@@ -20942,7 +21095,7 @@
       <c r="J405" s="3"/>
       <c r="K405" s="3"/>
     </row>
-    <row r="406" spans="1:11" ht="304.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:11" ht="304.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A406" s="3" t="s">
         <v>2148</v>
       </c>
@@ -20969,7 +21122,7 @@
       <c r="J406" s="3"/>
       <c r="K406" s="3"/>
     </row>
-    <row r="407" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A407" s="3" t="s">
         <v>2154</v>
       </c>
@@ -20996,7 +21149,7 @@
       <c r="J407" s="3"/>
       <c r="K407" s="3"/>
     </row>
-    <row r="408" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A408" s="3" t="s">
         <v>2159</v>
       </c>
@@ -21021,7 +21174,7 @@
       <c r="J408" s="3"/>
       <c r="K408" s="3"/>
     </row>
-    <row r="409" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A409" s="3" t="s">
         <v>2163</v>
       </c>
@@ -21048,7 +21201,7 @@
       <c r="J409" s="3"/>
       <c r="K409" s="3"/>
     </row>
-    <row r="410" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A410" s="3" t="s">
         <v>2169</v>
       </c>
@@ -21075,7 +21228,7 @@
       <c r="J410" s="3"/>
       <c r="K410" s="3"/>
     </row>
-    <row r="411" spans="1:11" ht="304.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:11" ht="304.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A411" s="3" t="s">
         <v>2174</v>
       </c>
@@ -21102,7 +21255,7 @@
       <c r="J411" s="3"/>
       <c r="K411" s="3"/>
     </row>
-    <row r="412" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A412" s="3" t="s">
         <v>2179</v>
       </c>
@@ -21129,7 +21282,7 @@
       <c r="J412" s="3"/>
       <c r="K412" s="3"/>
     </row>
-    <row r="413" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A413" s="3" t="s">
         <v>2185</v>
       </c>
@@ -21156,7 +21309,7 @@
       <c r="J413" s="3"/>
       <c r="K413" s="3"/>
     </row>
-    <row r="414" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A414" s="3" t="s">
         <v>2191</v>
       </c>
@@ -21183,7 +21336,7 @@
       <c r="J414" s="3"/>
       <c r="K414" s="3"/>
     </row>
-    <row r="415" spans="1:11" ht="275.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:11" ht="275.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A415" s="3" t="s">
         <v>2196</v>
       </c>
@@ -21210,7 +21363,7 @@
       <c r="J415" s="3"/>
       <c r="K415" s="3"/>
     </row>
-    <row r="416" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A416" s="3" t="s">
         <v>2201</v>
       </c>
@@ -21237,7 +21390,7 @@
       <c r="J416" s="3"/>
       <c r="K416" s="3"/>
     </row>
-    <row r="417" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A417" s="3" t="s">
         <v>2207</v>
       </c>
@@ -21264,7 +21417,7 @@
       <c r="J417" s="3"/>
       <c r="K417" s="3"/>
     </row>
-    <row r="418" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A418" s="3" t="s">
         <v>2213</v>
       </c>
@@ -21289,7 +21442,7 @@
       <c r="J418" s="3"/>
       <c r="K418" s="3"/>
     </row>
-    <row r="419" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A419" s="3" t="s">
         <v>2217</v>
       </c>
@@ -21316,7 +21469,7 @@
       <c r="J419" s="3"/>
       <c r="K419" s="3"/>
     </row>
-    <row r="420" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A420" s="3" t="s">
         <v>2222</v>
       </c>
@@ -21341,7 +21494,7 @@
       <c r="J420" s="3"/>
       <c r="K420" s="3"/>
     </row>
-    <row r="421" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A421" s="3" t="s">
         <v>2226</v>
       </c>
@@ -21368,7 +21521,7 @@
       <c r="J421" s="3"/>
       <c r="K421" s="3"/>
     </row>
-    <row r="422" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A422" s="3" t="s">
         <v>2231</v>
       </c>
@@ -21393,7 +21546,7 @@
       <c r="J422" s="3"/>
       <c r="K422" s="3"/>
     </row>
-    <row r="423" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A423" s="3" t="s">
         <v>2236</v>
       </c>
@@ -21420,7 +21573,7 @@
       <c r="J423" s="3"/>
       <c r="K423" s="3"/>
     </row>
-    <row r="424" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A424" s="3" t="s">
         <v>2241</v>
       </c>
@@ -21445,7 +21598,7 @@
       <c r="J424" s="3"/>
       <c r="K424" s="3"/>
     </row>
-    <row r="425" spans="1:11" ht="362.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:11" ht="362.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A425" s="3" t="s">
         <v>2246</v>
       </c>
@@ -21472,7 +21625,7 @@
       <c r="J425" s="3"/>
       <c r="K425" s="3"/>
     </row>
-    <row r="426" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A426" s="3" t="s">
         <v>2251</v>
       </c>
@@ -21499,7 +21652,7 @@
       <c r="J426" s="3"/>
       <c r="K426" s="3"/>
     </row>
-    <row r="427" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A427" s="3" t="s">
         <v>2257</v>
       </c>
@@ -21526,7 +21679,7 @@
       <c r="J427" s="3"/>
       <c r="K427" s="3"/>
     </row>
-    <row r="428" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A428" s="3" t="s">
         <v>2262</v>
       </c>
@@ -21551,7 +21704,7 @@
       <c r="J428" s="3"/>
       <c r="K428" s="3"/>
     </row>
-    <row r="429" spans="1:11" ht="319.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:11" ht="319" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A429" s="3" t="s">
         <v>2267</v>
       </c>
@@ -21578,7 +21731,7 @@
       <c r="J429" s="3"/>
       <c r="K429" s="3"/>
     </row>
-    <row r="430" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A430" s="3" t="s">
         <v>2273</v>
       </c>
@@ -21605,7 +21758,7 @@
       <c r="J430" s="3"/>
       <c r="K430" s="3"/>
     </row>
-    <row r="431" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A431" s="3" t="s">
         <v>2278</v>
       </c>
@@ -21630,7 +21783,7 @@
       <c r="J431" s="3"/>
       <c r="K431" s="3"/>
     </row>
-    <row r="432" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A432" s="3" t="s">
         <v>2283</v>
       </c>
@@ -21655,7 +21808,7 @@
       <c r="J432" s="3"/>
       <c r="K432" s="3"/>
     </row>
-    <row r="433" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A433" s="3" t="s">
         <v>2287</v>
       </c>
@@ -21682,7 +21835,7 @@
       <c r="J433" s="3"/>
       <c r="K433" s="3"/>
     </row>
-    <row r="434" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A434" s="3" t="s">
         <v>2292</v>
       </c>
@@ -21709,7 +21862,7 @@
       <c r="J434" s="3"/>
       <c r="K434" s="3"/>
     </row>
-    <row r="435" spans="1:11" ht="333.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:11" ht="333.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A435" s="3" t="s">
         <v>2298</v>
       </c>
@@ -21736,7 +21889,7 @@
       <c r="J435" s="3"/>
       <c r="K435" s="3"/>
     </row>
-    <row r="436" spans="1:11" ht="275.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:11" ht="275.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A436" s="3" t="s">
         <v>2303</v>
       </c>
@@ -21763,7 +21916,7 @@
       <c r="J436" s="3"/>
       <c r="K436" s="3"/>
     </row>
-    <row r="437" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A437" s="3" t="s">
         <v>2308</v>
       </c>
@@ -21788,7 +21941,7 @@
       <c r="J437" s="3"/>
       <c r="K437" s="3"/>
     </row>
-    <row r="438" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A438" s="3" t="s">
         <v>2313</v>
       </c>
@@ -21813,7 +21966,7 @@
       <c r="J438" s="3"/>
       <c r="K438" s="3"/>
     </row>
-    <row r="439" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A439" s="3" t="s">
         <v>2318</v>
       </c>
@@ -21840,7 +21993,7 @@
       <c r="J439" s="3"/>
       <c r="K439" s="3"/>
     </row>
-    <row r="440" spans="1:11" ht="304.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:11" ht="304.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A440" s="3" t="s">
         <v>2323</v>
       </c>
@@ -21867,7 +22020,7 @@
       <c r="J440" s="3"/>
       <c r="K440" s="3"/>
     </row>
-    <row r="441" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A441" s="3" t="s">
         <v>2328</v>
       </c>
@@ -21894,7 +22047,7 @@
       <c r="J441" s="3"/>
       <c r="K441" s="3"/>
     </row>
-    <row r="442" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A442" s="3" t="s">
         <v>2334</v>
       </c>
@@ -21921,7 +22074,7 @@
       <c r="J442" s="3"/>
       <c r="K442" s="3"/>
     </row>
-    <row r="443" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A443" s="3" t="s">
         <v>2339</v>
       </c>
@@ -21948,7 +22101,7 @@
       <c r="J443" s="3"/>
       <c r="K443" s="3"/>
     </row>
-    <row r="444" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A444" s="3" t="s">
         <v>2344</v>
       </c>
@@ -21975,7 +22128,7 @@
       <c r="J444" s="3"/>
       <c r="K444" s="3"/>
     </row>
-    <row r="445" spans="1:11" ht="304.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:11" ht="304.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A445" s="3" t="s">
         <v>2350</v>
       </c>
@@ -22002,7 +22155,7 @@
       <c r="J445" s="3"/>
       <c r="K445" s="3"/>
     </row>
-    <row r="446" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A446" s="3" t="s">
         <v>2355</v>
       </c>
@@ -22029,7 +22182,7 @@
       <c r="J446" s="3"/>
       <c r="K446" s="3"/>
     </row>
-    <row r="447" spans="1:11" ht="409.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:11" ht="409.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A447" s="3" t="s">
         <v>2361</v>
       </c>
@@ -22056,7 +22209,7 @@
       <c r="J447" s="3"/>
       <c r="K447" s="3"/>
     </row>
-    <row r="448" spans="1:11" ht="319.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:11" ht="319" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A448" s="3" t="s">
         <v>2367</v>
       </c>
@@ -22083,7 +22236,7 @@
       <c r="J448" s="3"/>
       <c r="K448" s="3"/>
     </row>
-    <row r="449" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A449" s="3" t="s">
         <v>2372</v>
       </c>
@@ -22108,7 +22261,7 @@
       <c r="J449" s="3"/>
       <c r="K449" s="3"/>
     </row>
-    <row r="450" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A450" s="3" t="s">
         <v>2376</v>
       </c>
@@ -22135,7 +22288,7 @@
       <c r="J450" s="3"/>
       <c r="K450" s="3"/>
     </row>
-    <row r="451" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A451" s="3" t="s">
         <v>2381</v>
       </c>
@@ -22162,7 +22315,7 @@
       <c r="J451" s="3"/>
       <c r="K451" s="3"/>
     </row>
-    <row r="452" spans="1:11" ht="275.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:11" ht="275.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A452" s="3" t="s">
         <v>2387</v>
       </c>
@@ -22189,7 +22342,7 @@
       <c r="J452" s="3"/>
       <c r="K452" s="3"/>
     </row>
-    <row r="453" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A453" s="3" t="s">
         <v>2393</v>
       </c>
@@ -22214,7 +22367,7 @@
       <c r="J453" s="3"/>
       <c r="K453" s="3"/>
     </row>
-    <row r="454" spans="1:11" ht="333.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:11" ht="333.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A454" s="3" t="s">
         <v>2397</v>
       </c>
@@ -22241,7 +22394,7 @@
       <c r="J454" s="3"/>
       <c r="K454" s="3"/>
     </row>
-    <row r="455" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A455" s="3" t="s">
         <v>2403</v>
       </c>
@@ -22268,7 +22421,7 @@
       <c r="J455" s="3"/>
       <c r="K455" s="3"/>
     </row>
-    <row r="456" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A456" s="3" t="s">
         <v>2408</v>
       </c>
@@ -22295,7 +22448,7 @@
       <c r="J456" s="3"/>
       <c r="K456" s="3"/>
     </row>
-    <row r="457" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A457" s="3" t="s">
         <v>2413</v>
       </c>
@@ -22322,7 +22475,7 @@
       <c r="J457" s="3"/>
       <c r="K457" s="3"/>
     </row>
-    <row r="458" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A458" s="3" t="s">
         <v>2419</v>
       </c>
@@ -22347,7 +22500,7 @@
       <c r="J458" s="3"/>
       <c r="K458" s="3"/>
     </row>
-    <row r="459" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A459" s="3" t="s">
         <v>2423</v>
       </c>
@@ -22372,7 +22525,7 @@
       <c r="J459" s="3"/>
       <c r="K459" s="3"/>
     </row>
-    <row r="460" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A460" s="3" t="s">
         <v>2427</v>
       </c>
@@ -22395,7 +22548,7 @@
       <c r="J460" s="3"/>
       <c r="K460" s="3"/>
     </row>
-    <row r="461" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A461" s="3" t="s">
         <v>2431</v>
       </c>
@@ -22422,7 +22575,7 @@
       <c r="J461" s="3"/>
       <c r="K461" s="3"/>
     </row>
-    <row r="462" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A462" s="3" t="s">
         <v>2437</v>
       </c>
@@ -22449,7 +22602,7 @@
       <c r="J462" s="3"/>
       <c r="K462" s="3"/>
     </row>
-    <row r="463" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A463" s="3" t="s">
         <v>2443</v>
       </c>
@@ -22476,7 +22629,7 @@
       <c r="J463" s="3"/>
       <c r="K463" s="3"/>
     </row>
-    <row r="464" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A464" s="3" t="s">
         <v>2449</v>
       </c>
@@ -22503,7 +22656,7 @@
       <c r="J464" s="3"/>
       <c r="K464" s="3"/>
     </row>
-    <row r="465" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A465" s="3" t="s">
         <v>2455</v>
       </c>
@@ -22530,7 +22683,7 @@
       <c r="J465" s="3"/>
       <c r="K465" s="3"/>
     </row>
-    <row r="466" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A466" s="3" t="s">
         <v>2460</v>
       </c>
@@ -22557,7 +22710,7 @@
       <c r="J466" s="3"/>
       <c r="K466" s="3"/>
     </row>
-    <row r="467" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A467" s="3" t="s">
         <v>2466</v>
       </c>
@@ -22584,7 +22737,7 @@
       <c r="J467" s="3"/>
       <c r="K467" s="3"/>
     </row>
-    <row r="468" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A468" s="3" t="s">
         <v>2472</v>
       </c>
@@ -22611,7 +22764,7 @@
       <c r="J468" s="3"/>
       <c r="K468" s="3"/>
     </row>
-    <row r="469" spans="1:11" ht="409.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:11" ht="409.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A469" s="3" t="s">
         <v>2477</v>
       </c>
@@ -22638,7 +22791,7 @@
       <c r="J469" s="3"/>
       <c r="K469" s="3"/>
     </row>
-    <row r="470" spans="1:11" ht="333.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:11" ht="333.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A470" s="3" t="s">
         <v>2483</v>
       </c>
@@ -22663,7 +22816,7 @@
       <c r="J470" s="3"/>
       <c r="K470" s="3"/>
     </row>
-    <row r="471" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A471" s="3" t="s">
         <v>2488</v>
       </c>
@@ -22688,7 +22841,7 @@
       <c r="J471" s="3"/>
       <c r="K471" s="3"/>
     </row>
-    <row r="472" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A472" s="3" t="s">
         <v>2492</v>
       </c>
@@ -22715,7 +22868,7 @@
       <c r="J472" s="3"/>
       <c r="K472" s="3"/>
     </row>
-    <row r="473" spans="1:11" ht="333.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:11" ht="333.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A473" s="3" t="s">
         <v>2498</v>
       </c>
@@ -22742,7 +22895,7 @@
       <c r="J473" s="3"/>
       <c r="K473" s="3"/>
     </row>
-    <row r="474" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A474" s="3" t="s">
         <v>2504</v>
       </c>
@@ -22769,7 +22922,7 @@
       <c r="J474" s="3"/>
       <c r="K474" s="3"/>
     </row>
-    <row r="475" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A475" s="3" t="s">
         <v>2510</v>
       </c>
@@ -22796,7 +22949,7 @@
       <c r="J475" s="3"/>
       <c r="K475" s="3"/>
     </row>
-    <row r="476" spans="1:11" ht="275.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:11" ht="275.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A476" s="3" t="s">
         <v>2515</v>
       </c>
@@ -22823,7 +22976,7 @@
       <c r="J476" s="3"/>
       <c r="K476" s="3"/>
     </row>
-    <row r="477" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A477" s="3" t="s">
         <v>2520</v>
       </c>
@@ -22848,7 +23001,7 @@
       <c r="J477" s="3"/>
       <c r="K477" s="3"/>
     </row>
-    <row r="478" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A478" s="3" t="s">
         <v>2524</v>
       </c>
@@ -22875,7 +23028,7 @@
       <c r="J478" s="3"/>
       <c r="K478" s="3"/>
     </row>
-    <row r="479" spans="1:11" ht="319.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:11" ht="319" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A479" s="3" t="s">
         <v>2529</v>
       </c>
@@ -22902,7 +23055,7 @@
       <c r="J479" s="3"/>
       <c r="K479" s="3"/>
     </row>
-    <row r="480" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A480" s="3" t="s">
         <v>2534</v>
       </c>
@@ -22927,7 +23080,7 @@
       <c r="J480" s="3"/>
       <c r="K480" s="3"/>
     </row>
-    <row r="481" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A481" s="3" t="s">
         <v>2538</v>
       </c>
@@ -22954,7 +23107,7 @@
       <c r="J481" s="3"/>
       <c r="K481" s="3"/>
     </row>
-    <row r="482" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A482" s="3" t="s">
         <v>2543</v>
       </c>
@@ -22979,7 +23132,7 @@
       <c r="J482" s="3"/>
       <c r="K482" s="3"/>
     </row>
-    <row r="483" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A483" s="3" t="s">
         <v>2548</v>
       </c>
@@ -23004,7 +23157,7 @@
       <c r="J483" s="3"/>
       <c r="K483" s="3"/>
     </row>
-    <row r="484" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A484" s="3" t="s">
         <v>2552</v>
       </c>
@@ -23031,7 +23184,7 @@
       <c r="J484" s="3"/>
       <c r="K484" s="3"/>
     </row>
-    <row r="485" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A485" s="3" t="s">
         <v>2557</v>
       </c>
@@ -23056,7 +23209,7 @@
       <c r="J485" s="3"/>
       <c r="K485" s="3"/>
     </row>
-    <row r="486" spans="1:11" ht="115.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:11" ht="116" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A486" s="3" t="s">
         <v>2561</v>
       </c>
@@ -23081,7 +23234,7 @@
       <c r="J486" s="3"/>
       <c r="K486" s="3"/>
     </row>
-    <row r="487" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A487" s="3" t="s">
         <v>2566</v>
       </c>
@@ -23108,7 +23261,7 @@
       <c r="J487" s="3"/>
       <c r="K487" s="3"/>
     </row>
-    <row r="488" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A488" s="3" t="s">
         <v>2572</v>
       </c>
@@ -23135,7 +23288,7 @@
       <c r="J488" s="3"/>
       <c r="K488" s="3"/>
     </row>
-    <row r="489" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A489" s="3" t="s">
         <v>2578</v>
       </c>
@@ -23158,7 +23311,7 @@
       <c r="J489" s="3"/>
       <c r="K489" s="3"/>
     </row>
-    <row r="490" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A490" s="3" t="s">
         <v>2581</v>
       </c>
@@ -23185,7 +23338,7 @@
       <c r="J490" s="3"/>
       <c r="K490" s="3"/>
     </row>
-    <row r="491" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A491" s="3" t="s">
         <v>2586</v>
       </c>
@@ -23212,7 +23365,7 @@
       <c r="J491" s="3"/>
       <c r="K491" s="3"/>
     </row>
-    <row r="492" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A492" s="3" t="s">
         <v>2592</v>
       </c>
@@ -23239,7 +23392,7 @@
       <c r="J492" s="3"/>
       <c r="K492" s="3"/>
     </row>
-    <row r="493" spans="1:11" ht="409.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:11" ht="409.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A493" s="3" t="s">
         <v>2597</v>
       </c>
@@ -23266,7 +23419,7 @@
       <c r="J493" s="3"/>
       <c r="K493" s="3"/>
     </row>
-    <row r="494" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A494" s="3" t="s">
         <v>2603</v>
       </c>
@@ -23293,7 +23446,7 @@
       <c r="J494" s="3"/>
       <c r="K494" s="3"/>
     </row>
-    <row r="495" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A495" s="3" t="s">
         <v>2609</v>
       </c>
@@ -23318,7 +23471,7 @@
       <c r="J495" s="3"/>
       <c r="K495" s="3"/>
     </row>
-    <row r="496" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A496" s="3" t="s">
         <v>2613</v>
       </c>
@@ -23343,7 +23496,7 @@
       <c r="J496" s="3"/>
       <c r="K496" s="3"/>
     </row>
-    <row r="497" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A497" s="3" t="s">
         <v>2617</v>
       </c>
@@ -23370,7 +23523,7 @@
       <c r="J497" s="3"/>
       <c r="K497" s="3"/>
     </row>
-    <row r="498" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A498" s="3" t="s">
         <v>2622</v>
       </c>
@@ -23395,7 +23548,7 @@
       <c r="J498" s="3"/>
       <c r="K498" s="3"/>
     </row>
-    <row r="499" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A499" s="3" t="s">
         <v>2627</v>
       </c>
@@ -23422,7 +23575,7 @@
       <c r="J499" s="3"/>
       <c r="K499" s="3"/>
     </row>
-    <row r="500" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A500" s="3" t="s">
         <v>2632</v>
       </c>
@@ -23449,7 +23602,7 @@
       <c r="J500" s="3"/>
       <c r="K500" s="3"/>
     </row>
-    <row r="501" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A501" s="3" t="s">
         <v>2638</v>
       </c>
@@ -23476,7 +23629,7 @@
       <c r="J501" s="3"/>
       <c r="K501" s="3"/>
     </row>
-    <row r="502" spans="1:11" ht="87" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:11" ht="87" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A502" s="3" t="s">
         <v>2643</v>
       </c>
@@ -23503,7 +23656,7 @@
       <c r="J502" s="3"/>
       <c r="K502" s="3"/>
     </row>
-    <row r="503" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A503" s="3" t="s">
         <v>2648</v>
       </c>
@@ -23530,7 +23683,7 @@
       <c r="J503" s="3"/>
       <c r="K503" s="3"/>
     </row>
-    <row r="504" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A504" s="3" t="s">
         <v>2653</v>
       </c>
@@ -23555,7 +23708,7 @@
       <c r="J504" s="3"/>
       <c r="K504" s="3"/>
     </row>
-    <row r="505" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A505" s="3" t="s">
         <v>2657</v>
       </c>
@@ -23582,7 +23735,7 @@
       <c r="J505" s="3"/>
       <c r="K505" s="3"/>
     </row>
-    <row r="506" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A506" s="3" t="s">
         <v>2662</v>
       </c>
@@ -23609,7 +23762,7 @@
       <c r="J506" s="3"/>
       <c r="K506" s="3"/>
     </row>
-    <row r="507" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A507" s="3" t="s">
         <v>2667</v>
       </c>
@@ -23636,7 +23789,7 @@
       <c r="J507" s="3"/>
       <c r="K507" s="3"/>
     </row>
-    <row r="508" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A508" s="3" t="s">
         <v>2672</v>
       </c>
@@ -23663,7 +23816,7 @@
       <c r="J508" s="3"/>
       <c r="K508" s="3"/>
     </row>
-    <row r="509" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A509" s="3" t="s">
         <v>2677</v>
       </c>
@@ -23690,7 +23843,7 @@
       <c r="J509" s="3"/>
       <c r="K509" s="3"/>
     </row>
-    <row r="510" spans="1:11" ht="289.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:11" ht="290" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A510" s="3" t="s">
         <v>2682</v>
       </c>
@@ -23717,7 +23870,7 @@
       <c r="J510" s="3"/>
       <c r="K510" s="3"/>
     </row>
-    <row r="511" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A511" s="3" t="s">
         <v>2688</v>
       </c>
@@ -23744,7 +23897,7 @@
       <c r="J511" s="3"/>
       <c r="K511" s="3"/>
     </row>
-    <row r="512" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A512" s="3" t="s">
         <v>2694</v>
       </c>
@@ -23769,7 +23922,7 @@
       <c r="J512" s="3"/>
       <c r="K512" s="3"/>
     </row>
-    <row r="513" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A513" s="3" t="s">
         <v>2698</v>
       </c>
@@ -23796,7 +23949,7 @@
       <c r="J513" s="3"/>
       <c r="K513" s="3"/>
     </row>
-    <row r="514" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A514" s="3" t="s">
         <v>2703</v>
       </c>
@@ -23823,7 +23976,7 @@
       <c r="J514" s="3"/>
       <c r="K514" s="3"/>
     </row>
-    <row r="515" spans="1:11" ht="289.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:11" ht="290" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A515" s="3" t="s">
         <v>2709</v>
       </c>
@@ -23850,7 +24003,7 @@
       <c r="J515" s="3"/>
       <c r="K515" s="3"/>
     </row>
-    <row r="516" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A516" s="3" t="s">
         <v>2714</v>
       </c>
@@ -23877,7 +24030,7 @@
       <c r="J516" s="3"/>
       <c r="K516" s="3"/>
     </row>
-    <row r="517" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A517" s="3" t="s">
         <v>2720</v>
       </c>
@@ -23904,7 +24057,7 @@
       <c r="J517" s="3"/>
       <c r="K517" s="3"/>
     </row>
-    <row r="518" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A518" s="3" t="s">
         <v>2725</v>
       </c>
@@ -23929,7 +24082,7 @@
       <c r="J518" s="3"/>
       <c r="K518" s="3"/>
     </row>
-    <row r="519" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A519" s="3" t="s">
         <v>2729</v>
       </c>
@@ -23956,7 +24109,7 @@
       <c r="J519" s="3"/>
       <c r="K519" s="3"/>
     </row>
-    <row r="520" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A520" s="3" t="s">
         <v>2735</v>
       </c>
@@ -23983,7 +24136,7 @@
       <c r="J520" s="3"/>
       <c r="K520" s="3"/>
     </row>
-    <row r="521" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A521" s="3" t="s">
         <v>2741</v>
       </c>
@@ -24010,7 +24163,7 @@
       <c r="J521" s="3"/>
       <c r="K521" s="3"/>
     </row>
-    <row r="522" spans="1:11" ht="348" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:11" ht="348" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A522" s="3" t="s">
         <v>2747</v>
       </c>
@@ -24037,7 +24190,7 @@
       <c r="J522" s="3"/>
       <c r="K522" s="3"/>
     </row>
-    <row r="523" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A523" s="3" t="s">
         <v>2752</v>
       </c>
@@ -24064,7 +24217,7 @@
       <c r="J523" s="3"/>
       <c r="K523" s="3"/>
     </row>
-    <row r="524" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A524" s="3" t="s">
         <v>2758</v>
       </c>
@@ -24091,7 +24244,7 @@
       <c r="J524" s="3"/>
       <c r="K524" s="3"/>
     </row>
-    <row r="525" spans="1:11" ht="391.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:11" ht="391.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A525" s="3" t="s">
         <v>2763</v>
       </c>
@@ -24118,7 +24271,7 @@
       <c r="J525" s="3"/>
       <c r="K525" s="3"/>
     </row>
-    <row r="526" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A526" s="3" t="s">
         <v>2769</v>
       </c>
@@ -24145,7 +24298,7 @@
       <c r="J526" s="3"/>
       <c r="K526" s="3"/>
     </row>
-    <row r="527" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A527" s="3" t="s">
         <v>2775</v>
       </c>
@@ -24172,7 +24325,7 @@
       <c r="J527" s="3"/>
       <c r="K527" s="3"/>
     </row>
-    <row r="528" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A528" s="3" t="s">
         <v>2780</v>
       </c>
@@ -24199,7 +24352,7 @@
       <c r="J528" s="3"/>
       <c r="K528" s="3"/>
     </row>
-    <row r="529" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A529" s="3" t="s">
         <v>2786</v>
       </c>
@@ -24226,7 +24379,7 @@
       <c r="J529" s="3"/>
       <c r="K529" s="3"/>
     </row>
-    <row r="530" spans="1:11" ht="87" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:11" ht="87" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A530" s="3" t="s">
         <v>2791</v>
       </c>
@@ -24249,7 +24402,7 @@
       <c r="J530" s="3"/>
       <c r="K530" s="3"/>
     </row>
-    <row r="531" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A531" s="3" t="s">
         <v>2795</v>
       </c>
@@ -24276,7 +24429,7 @@
       <c r="J531" s="3"/>
       <c r="K531" s="3"/>
     </row>
-    <row r="532" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A532" s="3" t="s">
         <v>2800</v>
       </c>
@@ -24303,7 +24456,7 @@
       <c r="J532" s="3"/>
       <c r="K532" s="3"/>
     </row>
-    <row r="533" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A533" s="3" t="s">
         <v>2805</v>
       </c>
@@ -24330,7 +24483,7 @@
       <c r="J533" s="3"/>
       <c r="K533" s="3"/>
     </row>
-    <row r="534" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A534" s="3" t="s">
         <v>2810</v>
       </c>
@@ -24357,7 +24510,7 @@
       <c r="J534" s="3"/>
       <c r="K534" s="3"/>
     </row>
-    <row r="535" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A535" s="3" t="s">
         <v>2815</v>
       </c>
@@ -24384,7 +24537,7 @@
       <c r="J535" s="3"/>
       <c r="K535" s="3"/>
     </row>
-    <row r="536" spans="1:11" ht="275.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:11" ht="275.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A536" s="3" t="s">
         <v>2820</v>
       </c>
@@ -24409,7 +24562,7 @@
       <c r="J536" s="3"/>
       <c r="K536" s="3"/>
     </row>
-    <row r="537" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A537" s="3" t="s">
         <v>2824</v>
       </c>
@@ -24436,7 +24589,7 @@
       <c r="J537" s="3"/>
       <c r="K537" s="3"/>
     </row>
-    <row r="538" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A538" s="3" t="s">
         <v>2830</v>
       </c>
@@ -24463,7 +24616,7 @@
       <c r="J538" s="3"/>
       <c r="K538" s="3"/>
     </row>
-    <row r="539" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A539" s="3" t="s">
         <v>2836</v>
       </c>
@@ -24490,7 +24643,7 @@
       <c r="J539" s="3"/>
       <c r="K539" s="3"/>
     </row>
-    <row r="540" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A540" s="3" t="s">
         <v>2842</v>
       </c>
@@ -24517,7 +24670,7 @@
       <c r="J540" s="3"/>
       <c r="K540" s="3"/>
     </row>
-    <row r="541" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A541" s="3" t="s">
         <v>2847</v>
       </c>
@@ -24544,7 +24697,7 @@
       <c r="J541" s="3"/>
       <c r="K541" s="3"/>
     </row>
-    <row r="542" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A542" s="3" t="s">
         <v>2852</v>
       </c>
@@ -24571,7 +24724,7 @@
       <c r="J542" s="3"/>
       <c r="K542" s="3"/>
     </row>
-    <row r="543" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A543" s="3" t="s">
         <v>2858</v>
       </c>
@@ -24596,7 +24749,7 @@
       <c r="J543" s="3"/>
       <c r="K543" s="3"/>
     </row>
-    <row r="544" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A544" s="3" t="s">
         <v>2862</v>
       </c>
@@ -24623,7 +24776,7 @@
       <c r="J544" s="3"/>
       <c r="K544" s="3"/>
     </row>
-    <row r="545" spans="1:11" ht="319.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:11" ht="319" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A545" s="3" t="s">
         <v>2867</v>
       </c>
@@ -24650,7 +24803,7 @@
       <c r="J545" s="3"/>
       <c r="K545" s="3"/>
     </row>
-    <row r="546" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A546" s="3" t="s">
         <v>2873</v>
       </c>
@@ -24677,7 +24830,7 @@
       <c r="J546" s="3"/>
       <c r="K546" s="3"/>
     </row>
-    <row r="547" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A547" s="3" t="s">
         <v>2878</v>
       </c>
@@ -24704,7 +24857,7 @@
       <c r="J547" s="3"/>
       <c r="K547" s="3"/>
     </row>
-    <row r="548" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A548" s="3" t="s">
         <v>2883</v>
       </c>
@@ -24729,7 +24882,7 @@
       <c r="J548" s="3"/>
       <c r="K548" s="3"/>
     </row>
-    <row r="549" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A549" s="3" t="s">
         <v>2887</v>
       </c>
@@ -24756,7 +24909,7 @@
       <c r="J549" s="3"/>
       <c r="K549" s="3"/>
     </row>
-    <row r="550" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A550" s="3" t="s">
         <v>2892</v>
       </c>
@@ -24783,7 +24936,7 @@
       <c r="J550" s="3"/>
       <c r="K550" s="3"/>
     </row>
-    <row r="551" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A551" s="3" t="s">
         <v>2897</v>
       </c>
@@ -24808,7 +24961,7 @@
       <c r="J551" s="3"/>
       <c r="K551" s="3"/>
     </row>
-    <row r="552" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A552" s="3" t="s">
         <v>2901</v>
       </c>
@@ -24835,7 +24988,7 @@
       <c r="J552" s="3"/>
       <c r="K552" s="3"/>
     </row>
-    <row r="553" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A553" s="3" t="s">
         <v>2907</v>
       </c>
@@ -24862,7 +25015,7 @@
       <c r="J553" s="3"/>
       <c r="K553" s="3"/>
     </row>
-    <row r="554" spans="1:11" ht="304.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:11" ht="304.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A554" s="3" t="s">
         <v>2912</v>
       </c>
@@ -24889,7 +25042,7 @@
       <c r="J554" s="3"/>
       <c r="K554" s="3"/>
     </row>
-    <row r="555" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A555" s="3" t="s">
         <v>2917</v>
       </c>
@@ -24916,7 +25069,7 @@
       <c r="J555" s="3"/>
       <c r="K555" s="3"/>
     </row>
-    <row r="556" spans="1:11" ht="115.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:11" ht="116" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A556" s="3" t="s">
         <v>2922</v>
       </c>
@@ -24943,7 +25096,7 @@
       <c r="J556" s="3"/>
       <c r="K556" s="3"/>
     </row>
-    <row r="557" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A557" s="3" t="s">
         <v>2928</v>
       </c>
@@ -24970,7 +25123,7 @@
       <c r="J557" s="3"/>
       <c r="K557" s="3"/>
     </row>
-    <row r="558" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A558" s="3" t="s">
         <v>2934</v>
       </c>
@@ -24997,7 +25150,7 @@
       <c r="J558" s="3"/>
       <c r="K558" s="3"/>
     </row>
-    <row r="559" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A559" s="3" t="s">
         <v>2940</v>
       </c>
@@ -25022,7 +25175,7 @@
       <c r="J559" s="3"/>
       <c r="K559" s="3"/>
     </row>
-    <row r="560" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A560" s="3" t="s">
         <v>2944</v>
       </c>
@@ -25047,7 +25200,7 @@
       <c r="J560" s="3"/>
       <c r="K560" s="3"/>
     </row>
-    <row r="561" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A561" s="3" t="s">
         <v>2948</v>
       </c>
@@ -25074,7 +25227,7 @@
       <c r="J561" s="3"/>
       <c r="K561" s="3"/>
     </row>
-    <row r="562" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A562" s="3" t="s">
         <v>2953</v>
       </c>
@@ -25101,7 +25254,7 @@
       <c r="J562" s="3"/>
       <c r="K562" s="3"/>
     </row>
-    <row r="563" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A563" s="3" t="s">
         <v>2959</v>
       </c>
@@ -25128,7 +25281,7 @@
       <c r="J563" s="3"/>
       <c r="K563" s="3"/>
     </row>
-    <row r="564" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A564" s="3" t="s">
         <v>2964</v>
       </c>
@@ -25155,7 +25308,7 @@
       <c r="J564" s="3"/>
       <c r="K564" s="3"/>
     </row>
-    <row r="565" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A565" s="3" t="s">
         <v>2969</v>
       </c>
@@ -25182,7 +25335,7 @@
       <c r="J565" s="3"/>
       <c r="K565" s="3"/>
     </row>
-    <row r="566" spans="1:11" ht="362.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:11" ht="362.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A566" s="3" t="s">
         <v>2974</v>
       </c>
@@ -25209,7 +25362,7 @@
       <c r="J566" s="3"/>
       <c r="K566" s="3"/>
     </row>
-    <row r="567" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A567" s="3" t="s">
         <v>2980</v>
       </c>
@@ -25236,7 +25389,7 @@
       <c r="J567" s="3"/>
       <c r="K567" s="3"/>
     </row>
-    <row r="568" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A568" s="3" t="s">
         <v>2985</v>
       </c>
@@ -25263,7 +25416,7 @@
       <c r="J568" s="3"/>
       <c r="K568" s="3"/>
     </row>
-    <row r="569" spans="1:11" ht="275.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:11" ht="275.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A569" s="3" t="s">
         <v>2990</v>
       </c>
@@ -25290,7 +25443,7 @@
       <c r="J569" s="3"/>
       <c r="K569" s="3"/>
     </row>
-    <row r="570" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A570" s="3" t="s">
         <v>2995</v>
       </c>
@@ -25317,7 +25470,7 @@
       <c r="J570" s="3"/>
       <c r="K570" s="3"/>
     </row>
-    <row r="571" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A571" s="3" t="s">
         <v>3000</v>
       </c>
@@ -25344,7 +25497,7 @@
       <c r="J571" s="3"/>
       <c r="K571" s="3"/>
     </row>
-    <row r="572" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A572" s="3" t="s">
         <v>3005</v>
       </c>
@@ -25371,7 +25524,7 @@
       <c r="J572" s="3"/>
       <c r="K572" s="3"/>
     </row>
-    <row r="573" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A573" s="3" t="s">
         <v>3010</v>
       </c>
@@ -25398,7 +25551,7 @@
       <c r="J573" s="3"/>
       <c r="K573" s="3"/>
     </row>
-    <row r="574" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A574" s="3" t="s">
         <v>3015</v>
       </c>
@@ -25425,7 +25578,7 @@
       <c r="J574" s="3"/>
       <c r="K574" s="3"/>
     </row>
-    <row r="575" spans="1:11" ht="232.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:11" ht="232" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A575" s="3" t="s">
         <v>3020</v>
       </c>
@@ -25452,7 +25605,7 @@
       <c r="J575" s="3"/>
       <c r="K575" s="3"/>
     </row>
-    <row r="576" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A576" s="3" t="s">
         <v>3025</v>
       </c>
@@ -25477,7 +25630,7 @@
       <c r="J576" s="3"/>
       <c r="K576" s="3"/>
     </row>
-    <row r="577" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A577" s="3" t="s">
         <v>3030</v>
       </c>
@@ -25504,7 +25657,7 @@
       <c r="J577" s="3"/>
       <c r="K577" s="3"/>
     </row>
-    <row r="578" spans="1:11" ht="145.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:11" ht="145" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A578" s="3" t="s">
         <v>3036</v>
       </c>
@@ -25531,7 +25684,7 @@
       <c r="J578" s="3"/>
       <c r="K578" s="3"/>
     </row>
-    <row r="579" spans="1:11" ht="275.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:11" ht="275.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A579" s="3" t="s">
         <v>3041</v>
       </c>
@@ -25558,7 +25711,7 @@
       <c r="J579" s="3"/>
       <c r="K579" s="3"/>
     </row>
-    <row r="580" spans="1:11" ht="304.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:11" ht="304.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A580" s="3" t="s">
         <v>3046</v>
       </c>
@@ -25585,7 +25738,7 @@
       <c r="J580" s="3"/>
       <c r="K580" s="3"/>
     </row>
-    <row r="581" spans="1:11" ht="188.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:11" ht="188.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A581" s="3" t="s">
         <v>3052</v>
       </c>
@@ -25612,7 +25765,7 @@
       <c r="J581" s="3"/>
       <c r="K581" s="3"/>
     </row>
-    <row r="582" spans="1:11" ht="275.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:11" ht="275.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A582" s="3" t="s">
         <v>3057</v>
       </c>
@@ -25639,7 +25792,7 @@
       <c r="J582" s="3"/>
       <c r="K582" s="3"/>
     </row>
-    <row r="583" spans="1:11" ht="304.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:11" ht="304.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A583" s="3" t="s">
         <v>3063</v>
       </c>
@@ -25664,7 +25817,7 @@
       <c r="J583" s="3"/>
       <c r="K583" s="3"/>
     </row>
-    <row r="584" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A584" s="3" t="s">
         <v>3067</v>
       </c>
@@ -25691,7 +25844,7 @@
       <c r="J584" s="3"/>
       <c r="K584" s="3"/>
     </row>
-    <row r="585" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A585" s="3" t="s">
         <v>3073</v>
       </c>
@@ -25716,7 +25869,7 @@
       <c r="J585" s="3"/>
       <c r="K585" s="3"/>
     </row>
-    <row r="586" spans="1:11" ht="333.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:11" ht="333.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A586" s="3" t="s">
         <v>3078</v>
       </c>
@@ -25743,7 +25896,7 @@
       <c r="J586" s="3"/>
       <c r="K586" s="3"/>
     </row>
-    <row r="587" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A587" s="3" t="s">
         <v>3083</v>
       </c>
@@ -25770,7 +25923,7 @@
       <c r="J587" s="3"/>
       <c r="K587" s="3"/>
     </row>
-    <row r="588" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A588" s="3" t="s">
         <v>3089</v>
       </c>
@@ -25797,7 +25950,7 @@
       <c r="J588" s="3"/>
       <c r="K588" s="3"/>
     </row>
-    <row r="589" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A589" s="3" t="s">
         <v>3094</v>
       </c>
@@ -25822,7 +25975,7 @@
       <c r="J589" s="3"/>
       <c r="K589" s="3"/>
     </row>
-    <row r="590" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A590" s="3" t="s">
         <v>3098</v>
       </c>
@@ -25847,7 +26000,7 @@
       <c r="J590" s="3"/>
       <c r="K590" s="3"/>
     </row>
-    <row r="591" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A591" s="3" t="s">
         <v>3102</v>
       </c>
@@ -25874,7 +26027,7 @@
       <c r="J591" s="3"/>
       <c r="K591" s="3"/>
     </row>
-    <row r="592" spans="1:11" ht="202.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:11" ht="203" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A592" s="3" t="s">
         <v>3108</v>
       </c>
@@ -25899,7 +26052,7 @@
       <c r="J592" s="3"/>
       <c r="K592" s="3"/>
     </row>
-    <row r="593" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A593" s="3" t="s">
         <v>3112</v>
       </c>
@@ -25926,7 +26079,7 @@
       <c r="J593" s="3"/>
       <c r="K593" s="3"/>
     </row>
-    <row r="594" spans="1:11" ht="304.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:11" ht="304.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A594" s="3" t="s">
         <v>3117</v>
       </c>
@@ -25953,7 +26106,7 @@
       <c r="J594" s="3"/>
       <c r="K594" s="3"/>
     </row>
-    <row r="595" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:11" ht="174" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A595" s="3" t="s">
         <v>3123</v>
       </c>
@@ -25980,7 +26133,7 @@
       <c r="J595" s="3"/>
       <c r="K595" s="3"/>
     </row>
-    <row r="596" spans="1:11" ht="246.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:11" ht="246.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A596" s="3" t="s">
         <v>3129</v>
       </c>
@@ -26007,7 +26160,7 @@
       <c r="J596" s="3"/>
       <c r="K596" s="3"/>
     </row>
-    <row r="597" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A597" s="3" t="s">
         <v>3135</v>
       </c>
@@ -26034,7 +26187,7 @@
       <c r="J597" s="3"/>
       <c r="K597" s="3"/>
     </row>
-    <row r="598" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:11" ht="130.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A598" s="3" t="s">
         <v>3141</v>
       </c>
@@ -26061,7 +26214,7 @@
       <c r="J598" s="3"/>
       <c r="K598" s="3"/>
     </row>
-    <row r="599" spans="1:11" ht="159.44999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:11" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A599" s="3" t="s">
         <v>3146</v>
       </c>
@@ -26088,7 +26241,7 @@
       <c r="J599" s="3"/>
       <c r="K599" s="3"/>
     </row>
-    <row r="600" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:11" ht="217.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A600" s="3" t="s">
         <v>3151</v>
       </c>
@@ -26115,7 +26268,7 @@
       <c r="J600" s="3"/>
       <c r="K600" s="3"/>
     </row>
-    <row r="601" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A601" s="3" t="s">
         <v>3157</v>
       </c>
@@ -26142,7 +26295,7 @@
       <c r="J601" s="3"/>
       <c r="K601" s="3"/>
     </row>
-    <row r="602" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:11" ht="261" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A602" s="3" t="s">
         <v>3162</v>
       </c>
@@ -26197,52 +26350,52 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>3168</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3169</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3170</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3171</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3172</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3173</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3174</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3175</v>
       </c>
